--- a/reviews/Boho_Blanket_PPC_Phase0_Review_2026-10-22.xlsx
+++ b/reviews/Boho_Blanket_PPC_Phase0_Review_2026-10-22.xlsx
@@ -10,12 +10,13 @@
   <sheets>
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Campaigns" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Spend Mix" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Placements" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Stop List" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Phase 0 Check" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Joseph Decisions" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Rules" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Optimize" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Spend Mix" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Placements" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Stop List" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Phase 0 Check" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Joseph Decisions" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Rules" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Campaigns!$A$5:$AX$45</definedName>
@@ -51,7 +52,197 @@
 </comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="G6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Measured: orders on Top of Search + product pages + rest of search, from Amazon's placement report at campaign grain (Ecotero Command Center, 24 Aug to 22 Oct).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Measured: orders on Top of Search + product pages + rest of search, from Amazon's placement report at campaign grain (Ecotero Command Center, 24 Aug to 22 Oct).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Measured: orders on Top of Search + product pages + rest of search, from Amazon's placement report at campaign grain (Ecotero Command Center, 24 Aug to 22 Oct).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Measured: orders on Top of Search + product pages + rest of search, from Amazon's placement report at campaign grain (Ecotero Command Center, 24 Aug to 22 Oct).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Measured: orders on Top of Search + product pages + rest of search, from Amazon's placement report at campaign grain (Ecotero Command Center, 24 Aug to 22 Oct).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Measured: orders on Top of Search + product pages + rest of search, from Amazon's placement report at campaign grain (Ecotero Command Center, 24 Aug to 22 Oct).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Measured: orders on Top of Search + product pages + rest of search, from Amazon's placement report at campaign grain (Ecotero Command Center, 24 Aug to 22 Oct).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Measured: orders on Top of Search + product pages + rest of search, from Amazon's placement report at campaign grain (Ecotero Command Center, 24 Aug to 22 Oct).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Measured: orders on Top of Search + product pages + rest of search, from Amazon's placement report at campaign grain (Ecotero Command Center, 24 Aug to 22 Oct).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Measured: orders on Top of Search + product pages + rest of search, from Amazon's placement report at campaign grain (Ecotero Command Center, 24 Aug to 22 Oct).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Measured: orders on Top of Search + product pages + rest of search, from Amazon's placement report at campaign grain (Ecotero Command Center, 24 Aug to 22 Oct).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Measured: orders on Top of Search + product pages + rest of search, from Amazon's placement report at campaign grain (Ecotero Command Center, 24 Aug to 22 Oct).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Measured: orders on Top of Search + product pages + rest of search, from Amazon's placement report at campaign grain (Ecotero Command Center, 24 Aug to 22 Oct).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Bid snapshot 22 Oct 2026, Ecotero Command Center.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Bid snapshot 22 Oct 2026, Ecotero Command Center.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -109,7 +300,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -132,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="567">
   <si>
     <t xml:space="preserve">Sleephoria Boho Throw Blanket: PPC stop list and Phase 0 check</t>
   </si>
@@ -149,7 +340,7 @@
     <t xml:space="preserve">Verdict</t>
   </si>
   <si>
-    <t xml:space="preserve">The stop list is mostly applied (7 of 9 paused). Phase 0 is not: 4 of the 5 boho core exact terms it says to run are paused, most of the last 15 days' spend went to campaigns outside Phase 0 (competitor product targeting and king or queen size terms), and the $25 a day cap is not set anywhere. No campaign is profitable at about 1% conversion; Phase 0 exists to cap the loss until the listing rebuild (target live 6 Nov), not to make money.</t>
+    <t xml:space="preserve">The stop list is mostly applied (7 of 9 paused). Phase 0 is not: 4 of the 5 boho core exact terms it says to run are paused, most of the last 15 days' spend went to campaigns outside Phase 0 (competitor product targeting and king or queen size terms), and the $25 a day cap is not set anywhere. No campaign is profitable at about 1% conversion; The fix: keep the 10 campaigns that get orders on Amazon and cut their bids to what a click is worth; pause the rest; cap the portfolio at $25 a day until the rebuilt listing goes live (6 Nov).</t>
   </si>
   <si>
     <t xml:space="preserve">Key numbers</t>
@@ -227,6 +418,12 @@
     <t xml:space="preserve">Stop-list items done</t>
   </si>
   <si>
+    <t xml:space="preserve">Keep set: estimated spend per week this cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimize tab; Phase 0 cap $175 a week</t>
+  </si>
+  <si>
     <t xml:space="preserve">Off-Amazon share of orders since launch</t>
   </si>
   <si>
@@ -260,28 +457,46 @@
     <t xml:space="preserve">8. The plan contradicts itself in places: 'throw blanket boho' is both a Phase 0 core term and on the stop list, and the hero term 'boho throw blanket' already meets the '20+ clicks, 0 orders' negate rule.</t>
   </si>
   <si>
-    <t xml:space="preserve">What to do now (Shayan, inside the plan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Pause every row marked 'Pause now' on the Campaigns tab (red): 7 competitor product-targeting campaigns, 4 king or queen size campaigns, the 2 stop-list leftovers, 'boho couch blanket', 'boho throw blankets for couch' and 4 small Phase 1 campaigns.</t>
+    <t xml:space="preserve">9. Every campaign is above break-even ACoS, including the ones that convert. Pausing them all would stop the orders; keeping them at today's bids keeps the loss. So the campaigns that get orders on Amazon stay on with bids cut to what a click is worth (Optimize tab).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The approach: keep what gets orders, optimize what costs too much</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only 10 campaigns have ever produced an order on Amazon (18 orders in total). They stay on, or come back on, and each gets bids set to what its clicks are worth (Optimize tab). Everything with 20+ on-Amazon clicks and no on-Amazon order is paused.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value of a click = target ACoS x average order value x conversion rate. The target ACoS is an input (default 38%, the plan's own pause line). Conversion is smoothed for small samples, so one lucky order does not set a high bid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top of Search converts about twice as well as an average click and product pages about half as well, so the base bid (paid on product pages) is set low and the Top of Search modifier carries the TOS bid. The data supports about +290%, inside the plan's +300% cap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bids move toward the target in the steps the team's rules allow (config/thresholds.yml): at most a 25% cut or 15% raise per 14-day cycle, and 20 points on the TOS modifier. Today's bids are 2 to 5 times what a click is worth, so this takes several cycles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to do now (Shayan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Pause every row marked 'Pause' on the Campaigns tab (red): 6 competitor product-targeting campaigns with no orders, the king and queen size campaigns, the 2 stop-list leftovers, 'boho couch blanket' and the small Phase 1 campaigns with no orders.</t>
   </si>
   <si>
     <t xml:space="preserve">2. Set a portfolio budget cap on 'SLEEPHORIA - Boho Blanket' so total spend cannot pass $25 a day, whatever gets re-enabled.</t>
   </si>
   <si>
-    <t xml:space="preserve">3. Brand defence: cut the Top of Search modifier from +380% to +300%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. 'bohemian throw blanket': lower the base bid from $0.52 to $0.45 and set Top of Search to +300%, so the money moves from product pages (0 orders) to Top of Search (converting). One lever per cycle, then leave it for 14 days (repo README principles 3 and 4).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Mark each change in the yellow 'Done?' column and post the summary in #boho-throw-blanket for Joseph.</t>
+    <t xml:space="preserve">3. Send Joseph the Optimize tab: the 'This cycle' base bids and TOS modifiers for the campaigns we keep, plus the re-enables. Most moves are larger than 15% or change a modifier, so they need his approval. Apply them once approved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Change nothing for 14 days after applying (repo README principle 4). Review on 5 Nov, the day before the rebuilt listing goes live.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Mark each change in the yellow 'Done?' columns and post the summary in #boho-throw-blanket.</t>
   </si>
   <si>
     <t xml:space="preserve">What Joseph decides (see Joseph Decisions tab)</t>
   </si>
   <si>
-    <t xml:space="preserve">Which boho core terms to re-enable ('boho throw', 'boho blanket', 'boho throw blanket'), whether 'bohemian blanket' comes back, what happens to 'boho king size blanket', and whether to drop 'throw blanket boho' from the core list. Also: why Off-Amazon stopped serving.</t>
+    <t xml:space="preserve">Approve the Optimize-tab bids; which paused campaigns with orders come back ('boho throw', 'boho blanket', 'bohemian blanket' and three small ones); whether the one converting competitor target (B0BLRBXBX5) stays on; the hero term 'boho throw blanket'; pausing 'boho king size blanket'; and why Off-Amazon stopped serving.</t>
   </si>
   <si>
     <t xml:space="preserve">How to use this workbook</t>
@@ -290,13 +505,16 @@
     <t xml:space="preserve">Campaigns: one row per campaign with settings, metrics for three windows, placement split, rule checks (formulas) and the recommended action. Filter on 'Recommended action' or 'Who decides'.</t>
   </si>
   <si>
+    <t xml:space="preserve">Optimize: the campaigns we keep, what a click is worth, this cycle's bids and TOS modifiers, expected weekly spend and orders, and the check against the $175 weekly cap.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Spend Mix: spend, clicks and orders by keyword family and by Phase 0 status.   Placements: where clicks and orders came from, and the Off-Amazon finding.</t>
   </si>
   <si>
     <t xml:space="preserve">Stop List: the 9 stop-list terms with live status.   Phase 0 Check: each Phase 0 element vs what is live.   Joseph Decisions: the open calls, with space to record them.</t>
   </si>
   <si>
-    <t xml:space="preserve">Rules: the thresholds and unit economics behind every check. Change a blue value there and all checks update.</t>
+    <t xml:space="preserve">Rules: the thresholds, unit economics and optimization inputs behind every check. Change a blue value there and everything updates.</t>
   </si>
   <si>
     <t xml:space="preserve">Data sources and caveats</t>
@@ -473,10 +691,10 @@
     <t xml:space="preserve">ENABLED</t>
   </si>
   <si>
-    <t xml:space="preserve">Joseph: pause, or reset to $0.20 base, TOS +0%, budget $3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kept in Phase 0 as the converting long tail at about $0.20 CPC. But 1,027 of its 1,063 clicks were Off-Amazon, which stopped in late September. On Amazon it has 0 orders; bid $0.97 x +413% = up to $4.98 a click; largest budget ($30).</t>
+    <t xml:space="preserve">Pause (Joseph): its orders were all Off-Amazon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 9 orders came from Off-Amazon traffic (1,027 of 1,063 clicks), which stopped in late September. On Amazon: 0 orders on 36 clicks; bid $0.97 x +413% = up to $4.98 a click; largest budget ($30).</t>
   </si>
   <si>
     <t xml:space="preserve">Joseph</t>
@@ -500,294 +718,300 @@
     <t xml:space="preserve">Not in Phase 0</t>
   </si>
   <si>
-    <t xml:space="preserve">Pause now (tell Joseph: listed in pack file 05 lane L1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not in the PDF's Phase 0 list. 5 orders on 476 clicks since launch (1.05%), under the 2% pause rule; 89% of its clicks were Off-Amazon.</t>
+    <t xml:space="preserve">Keep on; cut bid per Optimize tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Has an on-Amazon order (1 on 54 on-Amazon clicks); the other 4 of its 5 orders came Off-Amazon, which has stopped. ACoS 105%, so the bid comes down.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131359054806082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-boho blanket-Boho|Blanket|Core-MSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boho blanket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boho core</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 0: run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAUSED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph: re-enable at Optimize-tab bid, budget cut from $40 to $5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 0 says run it. 3 orders on Amazon (all from product pages), 1.6% CVR on 187 clicks; ACoS 156%, so only at a much lower bid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">271118311398471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-bohemian throw blanket-Boho|Blanket|Core-LSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bohemian throw blanket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep on; set bids per Optimize tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Getting orders (4 on Amazon since launch, 1 in the last 30 days) but ACoS 85%. Optimize: bids cut toward what a click is worth; TOS converts better than product pages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103168292442380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-B0BLRBXBX5-Exact-Conq-Fixed-SL-BOHO-BLANKET-BOUQUET-60x80-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B0BLRBXBX5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Competitor PAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BOHO-BLANKET-BOUQUET-60x80-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not in Phase 0 (Phase 1 lane L9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep on; cut bid per Optimize tab (Joseph: Phase 1 lane)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The only competitor target with an order (1 on 67 clicks). Paying $1.54 a click at Top of Search, so the bid comes down hard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143967856454663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-boho throw-Boho|Blanket|Core-MSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boho throw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph: re-enable at Optimize-tab bid, budget $5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 0 says run it. 3 orders on Amazon (all Top of Search), 2.4% CVR on 125 clicks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52789396358241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-throw blanket boho-Boho|Blanket|Core-MSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">throw blanket boho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 0: run AND stop list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep paused; remove from the core list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listed in both Phase 0 core and the stop list. 0 orders on 71 clicks since launch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143960123876477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-boho scandinavian cotton blanket-Boho|Blanket|Material-VLSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boho blanket throw cotton · boho cotton throw blanket · boho scandinavian cotton blanket +2 more keywords</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boho material (cotton)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph: re-enable at Optimize-tab bid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 order on Amazon on 62 on-Amazon clicks. Phase 1 material lane (L4) in the plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73752905509119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-boho blankets and throws-Boho|Blanket|Core-VLSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boho blankets and throws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 0: stop list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep paused (done)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stop list item. 0 orders on 72 clicks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140892082966699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-boho blanket king-Boho|Blanket|Size-VLSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-60x80-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boho blanket king</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exclude list (king / queen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pause now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Its 3 orders all came Off-Amazon (98 of 128 clicks). On Amazon: 0 orders on 30 clicks. King-size intent is on the exclude list; TOS +356%.</t>
   </si>
   <si>
     <t xml:space="preserve">Shayan</t>
   </si>
   <si>
-    <t xml:space="preserve">131359054806082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-boho blanket-Boho|Blanket|Core-MSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boho blanket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boho core</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 0: run</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAUSED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joseph decides: re-enable at low bid or keep paused</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 0 says run it, but 1.6% CVR on 187 clicks is under the 2% pause rule. Budget is $40 a day; cut to $5 if re-enabled.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">271118311398471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-bohemian throw blanket-Boho|Blanket|Core-LSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bohemian throw blanket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keep on; lower base bid to $0.45 and set TOS to +300%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only boho core exact term live. TOS converts (1 order on 8 clicks in 15 days) while product pages took 32 of 40 clicks with 0 orders. One lever only this cycle (repo README, principle 3).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103168292442380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-B0BLRBXBX5-Exact-Conq-Fixed-SL-BOHO-BLANKET-BOUQUET-60x80-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B0BLRBXBX5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Competitor PAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BOHO-BLANKET-BOUQUET-60x80-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not in Phase 0 (Phase 1 lane L9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pause now</t>
+    <t xml:space="preserve">274384612784893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-bohemian blanket-Boho|Blanket|Core-LSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bohemian blanket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stop list was built on September data. Since launch it is the best converter: 2 orders on 50 clicks (4.0%), both in the last 30 days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136479271696362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-boho throw blanket-Boho|Blanket|Core-MSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boho throw blanket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph decides: hero term, but 0 orders on 44 clicks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 0 hero term. It already meets the '20+ clicks, 0 orders' negate rule, so the plan contradicts itself. Budget $30 a day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153632991648836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-boho cotton blanket-Boho|Blanket|Material-VLSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boho cotton blanket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 order on Amazon on 35 clicks (Top of Search). Phase 1 material lane (L4) in the plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269303623430005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-throw blanket for couch boho-Boho|Blanket|Core-VLSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blanket boho · boho bed throw · boho blankets for bed +2 more keywords</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 order on Amazon on 26 on-Amazon clicks. Small sample.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">248203141513937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-king size boho blanket-Boho|Blanket|Size-VLSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-60x80-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">king size boho blanket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">King-size intent is on the exclude list. 0 orders on 23 clicks since launch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88375236561649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-boho picnic blanket-Boho|Blanket|Core-MSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boho picnic blanket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boho off-intent (picnic / beach / heated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stop list item still ENABLED. 0 orders on 18 clicks; TOS +330%; $12.14 budget.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201568460000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-boho blanket king size-Boho|Blanket|Size-VLSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-60x80-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boho blanket king size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep paused</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exclude list. 0 orders on 24 clicks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">199196980921698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-boho blanket throw-Boho|Blanket|Core-LSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boho blanket throw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stop list item. 0 orders on 32 clicks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158494562127971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-boho throw blanket for bed-Boho|Blanket|Core-LSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boho throw blanket for bed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stop list item. 0 orders on 28 clicks. Note: file 05 still lists it in lane L1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">264225421869119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL-BB-SP-B0FRF3JGK9-Exact-Conq-Fixed-SL-BOHO-BLANKET-BOUQUET-60x80-1-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B0FRF3JGK9</t>
   </si>
   <si>
     <t xml:space="preserve">Competitor product targeting is a Phase 1 lane (L9), not part of the Phase 0 hold.</t>
   </si>
   <si>
-    <t xml:space="preserve">143967856454663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-boho throw-Boho|Blanket|Core-MSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boho throw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joseph: re-enable at $0.45 to $0.50 base, TOS up to +300%, budget $5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 0 says run it. 2.4% CVR since launch on 125 clicks: inside the 2% to 4% 'hold at lower bid' band.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52789396358241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-throw blanket boho-Boho|Blanket|Core-MSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">throw blanket boho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 0: run AND stop list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keep paused; remove from the core list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Listed in both Phase 0 core and the stop list. 0 orders on 71 clicks since launch.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143960123876477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-boho scandinavian cotton blanket-Boho|Blanket|Material-VLSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boho blanket throw cotton · boho cotton throw blanket · boho scandinavian cotton blanket +2 more keywords</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boho material (cotton)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keep paused</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 1 material lane (L4). 1 order on 77 clicks.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73752905509119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-boho blankets and throws-Boho|Blanket|Core-VLSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boho blankets and throws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 0: stop list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keep paused (done)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stop list item. 0 orders on 72 clicks.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140892082966699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-boho blanket king-Boho|Blanket|Size-VLSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-60x80-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boho blanket king</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exclude list (king / queen)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">King-size intent is on the pack exclude list. 0 orders on its last 22 clicks; TOS +356%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274384612784893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-bohemian blanket-Boho|Blanket|Core-LSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bohemian blanket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joseph: re-enable at a low bid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stop list was built on September data. Since launch it is the best converter: 2 orders on 50 clicks (4.0%).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136479271696362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-boho throw blanket-Boho|Blanket|Core-MSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boho throw blanket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joseph decides: hero term, but 0 orders on 44 clicks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 0 hero term. It already meets the '20+ clicks, 0 orders' negate rule, so the plan contradicts itself. Budget $30 a day.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153632991648836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-boho cotton blanket-Boho|Blanket|Material-VLSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boho cotton blanket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 1 material lane (L4).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269303623430005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-throw blanket for couch boho-Boho|Blanket|Core-VLSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blanket boho · boho bed throw · boho blankets for bed +2 more keywords</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not in Phase 0. 1 order on 38 clicks.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">248203141513937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-king size boho blanket-Boho|Blanket|Size-VLSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-60x80-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">king size boho blanket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">King-size intent is on the exclude list. 0 orders on 23 clicks since launch.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88375236561649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-boho picnic blanket-Boho|Blanket|Core-MSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boho picnic blanket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boho off-intent (picnic / beach / heated)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stop list item still ENABLED. 0 orders on 18 clicks; TOS +330%; $12.14 budget.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201568460000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-boho blanket king size-Boho|Blanket|Size-VLSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-60x80-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boho blanket king size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exclude list. 0 orders on 24 clicks.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">199196980921698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-boho blanket throw-Boho|Blanket|Core-LSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boho blanket throw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stop list item. 0 orders on 32 clicks.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158494562127971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-boho throw blanket for bed-Boho|Blanket|Core-LSV-Exact-Rank-Fixed-SL-BOHO-BLANKET-BUTTERFLY-50x60-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boho throw blanket for bed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stop list item. 0 orders on 28 clicks. Note: file 05 still lists it in lane L1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">264225421869119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-BB-SP-B0FRF3JGK9-Exact-Conq-Fixed-SL-BOHO-BLANKET-BOUQUET-60x80-1-PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B0FRF3JGK9</t>
-  </si>
-  <si>
     <t xml:space="preserve">179711585918274</t>
   </si>
   <si>
@@ -911,10 +1135,7 @@
     <t xml:space="preserve">SL-BOHO-BLANKET-BOUQUET-50x60-1-PC</t>
   </si>
   <si>
-    <t xml:space="preserve">Pause now; revisit in Phase 1 (L2 design)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 order on 7 clicks since launch: too little data to judge. Phase 1 design lane.</t>
+    <t xml:space="preserve">1 order on 7 clicks since launch (Top of Search). Small sample, so the smoothed CVR keeps the bid modest.</t>
   </si>
   <si>
     <t xml:space="preserve">40188236585691</t>
@@ -1031,6 +1252,177 @@
     <t xml:space="preserve">TOTAL (all 40 campaigns)</t>
   </si>
   <si>
+    <t xml:space="preserve">Optimize: keep the campaigns that get orders on Amazon, and pay for each click only what it is worth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How it works: value of a click = target ACoS x average order value x conversion rate (smoothed for small samples). Top of Search converts about 2x an average click and product pages about half, so the base bid (product pages) and the TOS bid are set separately. Bids move toward the target in steps the team's rules allow: at most -25% / +15% on bids and 20 points on the TOS modifier per 14-day cycle. Inputs live on the Rules tab (blue). Yellow column is for you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since launch, on Amazon only (Off-Amazon has stopped)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What a click is worth (target)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This cycle (22 Oct to 5 Nov)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected per week this cycle (estimate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign-off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 0 status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-Amazon clicks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-Amazon orders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-Amazon spend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All orders since launch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales since launch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orders last 30 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg order value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-Amazon CVR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smoothed CVR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current CPC (on Amazon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACoS since launch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value of a click at target ACoS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target base bid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target TOS bid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target TOS modifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current base bid (avg CPC if not known)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base bid gap to target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base bid this cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change this cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current TOS modifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOS modifier this cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max TOS bid this cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clicks per week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend per week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orders per week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who approves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sleephoria boho throw blanket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 Nov 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boho scandinavian cotton blanket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">throw blanket for couch boho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rustic floral boho blanket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boho king size blanket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL for campaigns we keep or re-enable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly spend check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimated weekly spend of the keep set this cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 0 weekly cap (D4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headroom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimated orders per week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last 15 days actual, for comparison: spend per week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last 15 days actual: orders per week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reading the estimates: clicks per week assume the same click volume as since launch. Lower bids usually mean fewer clicks, so spend and orders will come in lower than shown, and ACoS should move toward the target.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why not break-even? At break-even ACoS (about 12.6%) a click is worth 3 to 10 cents, which would stop delivery. The target is an input on the Rules tab: try 0.25 or 0.50 there and the bids update.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why smoothing? 'rustic floral' has 1 order on 7 clicks (14% CVR). Smoothing adds 50 clicks at the product's average on-Amazon CVR, so one lucky order does not set a high bid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After this cycle: change nothing for 14 days (repo README principle 4). On 5 Nov, re-read clicks and orders. Where impressions collapsed and CVR held, raise bids by up to 15%; where ACoS is still above the target, take the next 25% step. The listing rebuild goes live on 6 Nov, so read the new CVR before the next move.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand defence is not bid down: own-brand clicks protect the listing and cost little. Only its TOS modifier steps toward the +300% cap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who approves: Shayan can move a bid by up to 15% on an enabled campaign. Larger moves, any TOS modifier change, re-enabling or pausing a campaign go to Joseph (config/thresholds.yml, authority section).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Where the money goes: spend, clicks and orders by keyword family</t>
   </si>
   <si>
@@ -1145,9 +1537,6 @@
     <t xml:space="preserve">Pack evidence (to 9 Sep)</t>
   </si>
   <si>
-    <t xml:space="preserve">State now</t>
-  </si>
-  <si>
     <t xml:space="preserve">Clicks since launch</t>
   </si>
   <si>
@@ -1160,9 +1549,6 @@
     <t xml:space="preserve">CVR since launch</t>
   </si>
   <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
     <t xml:space="preserve">Comment</t>
   </si>
   <si>
@@ -1331,7 +1717,7 @@
     <t xml:space="preserve">Product pages took about a third of spend and 0 orders in the last 15 days.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lower base bids where TOS converts (e.g. bohemian throw blanket $0.52 to $0.45, TOS to +300%)</t>
+    <t xml:space="preserve">Base bids set from what a product-page click is worth (Optimize tab); TOS modifier carries the TOS bid</t>
   </si>
   <si>
     <t xml:space="preserve">Everything else</t>
@@ -1355,9 +1741,6 @@
     <t xml:space="preserve">#</t>
   </si>
   <si>
-    <t xml:space="preserve">ACoS since launch</t>
-  </si>
-  <si>
     <t xml:space="preserve">Suggestion</t>
   </si>
   <si>
@@ -1367,40 +1750,61 @@
     <t xml:space="preserve">Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Re-enable at $0.45 to $0.50, TOS up to +300%, budget $5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only at a low bid, budget cut from $40 to $5; or keep paused (under 2% CVR)</t>
+    <t xml:space="preserve">Re-enable at the Optimize-tab bid, budget $5 (3 on-Amazon orders, all Top of Search)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-enable at the Optimize-tab bid, budget cut from $40 to $5 (3 on-Amazon orders)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-enable at the Optimize-tab bid: best CVR on the product, 2 orders in the last 30 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not in Phase 0 (Phase 1 L4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-enable at the Optimize-tab bid, or hold for Phase 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B0BLRBXBX5 (MSGKV 60x80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not in Phase 0 (Phase 1 L9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep on at the Optimize-tab bid (it converts), or pause until Phase 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bid cuts above 15% and TOS modifier changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager approval (thresholds.yml)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approve the 'This cycle' bids and modifiers on the Optimize tab in one go</t>
   </si>
   <si>
     <t xml:space="preserve">Run (hero term)</t>
   </si>
   <si>
-    <t xml:space="preserve">Joseph's call: plan says run, but it meets the 20+ clicks, 0 orders rule</t>
+    <t xml:space="preserve">Plan says run, but 0 orders on 44 clicks (meets the negate rule). Keep paused or test at the floor bid</t>
   </si>
   <si>
     <t xml:space="preserve">Run AND stop</t>
   </si>
   <si>
-    <t xml:space="preserve">Stop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re-enable at a low bid: best CVR on the product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boho king size blanket</t>
-  </si>
-  <si>
     <t xml:space="preserve">Run (long tail)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pause, or $0.20 base, TOS +0%, budget $3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not in PDF Phase 0; L1 in pack file 05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pause (1.05% CVR on 476 clicks)</t>
+    <t xml:space="preserve">Pause: all 9 orders came Off-Amazon; 0 on 36 on-Amazon clicks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Off-Amazon placement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find out why it stopped serving in late September; it brought about half of all orders at $0.20 a click</t>
   </si>
   <si>
     <t xml:space="preserve">Fill in the yellow Decision and Date cells after Joseph decides. Example: Decision 'Re-enable at $0.45, TOS +300%', Date '23 Oct'.</t>
@@ -1502,6 +1906,54 @@
     <t xml:space="preserve">Pack file 08, ESTIMATE until D8</t>
   </si>
   <si>
+    <t xml:space="preserve">OPTIMIZE: target ACoS for campaigns we keep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default = the plan's own pause line (3x break-even, about 38%). Break-even (12.6%) would push bids to a few cents and stop traffic. Change it here to test other targets.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTIMIZE: smoothing weight (clicks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small samples are pulled toward the product's on-Amazon CVR as if this many extra clicks had been seen. Stops 1 order on 7 clicks reading as 14% CVR.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTIMIZE: max bid cut per cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">config/thresholds.yml W5_bids correction_step_pct (25%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTIMIZE: max bid raise per cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">config/thresholds.yml W5_bids routine_step_pct (15%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTIMIZE: max TOS modifier change per cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">config/thresholds.yml W6_placement max_step_points (20 points per 14 days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTIMIZE: lowest base bid we set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floor so a campaign keeps some delivery. Amazon's minimum is $0.02.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTIMIZE: specialist bid authority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">config/thresholds.yml authority bid_pct specialist (15%); larger moves and any placement change go to the manager (Joseph)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTIMIZE: ad days since launch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ads live 26 Aug to 22 Oct 2026, used to turn since-launch clicks into clicks per week</t>
+  </si>
+  <si>
     <t xml:space="preserve">Derived (formulas)</t>
   </si>
   <si>
@@ -1545,6 +1997,30 @@
   </si>
   <si>
     <t xml:space="preserve">CVR needed to break even at last-15-day CPC, 60x80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTIMIZE: product on-Amazon CVR since launch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orders / clicks on Top of Search, product pages and rest of search. Used as the smoothing prior.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTIMIZE: Top of Search CVR factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOS CVR / on-Amazon CVR. A TOS click is worth this many times an average click.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTIMIZE: product page CVR factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product-page CVR / on-Amazon CVR. The base bid (which product pages pay) is set at this share of a click's value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTIMIZE: TOS modifier the data supports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOS factor / product page factor - 1, capped at the plan's +300%</t>
   </si>
   <si>
     <t xml:space="preserve">Note: contribution uses off-peak storage ($0.20 a unit). Peak storage (1 Oct to 31 Dec, $2.40 per cu ft) is about $0.62 a unit, so Q4 contribution is closer to $3.02 and $3.95 and break-even ACoS about 11%.</t>
@@ -1554,7 +2030,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
@@ -1562,8 +2038,10 @@
     <numFmt numFmtId="168" formatCode="@"/>
     <numFmt numFmtId="169" formatCode="0%"/>
     <numFmt numFmtId="170" formatCode="0.00"/>
-    <numFmt numFmtId="171" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
-    <numFmt numFmtId="172" formatCode="0.0\x"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="172" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+    <numFmt numFmtId="173" formatCode="0.0\x"/>
+    <numFmt numFmtId="174" formatCode="0.00\x"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -1740,7 +2218,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="54">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1865,6 +2343,22 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1901,7 +2395,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1921,7 +2415,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1930,6 +2424,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2079,7 +2581,7 @@
       <rgbColor rgb="FF595959"/>
       <rgbColor rgb="FFA6A6A6"/>
       <rgbColor rgb="FF1F3864"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF70AD47"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -2276,7 +2778,7 @@
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
@@ -2317,7 +2819,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
@@ -2561,36 +3063,38 @@
       <c r="A24" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="13" t="n">
+      <c r="B24" s="12" t="n">
+        <f aca="false">Optimize!AD19</f>
+        <v>65.8413362068966</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="13" t="n">
         <f aca="false">IF(Placements!D9=0,0,Placements!D8/Placements!D9)</f>
         <v>0.470588235294118</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -2602,7 +3106,7 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -2614,7 +3118,7 @@
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -2624,9 +3128,9 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -2636,9 +3140,9 @@
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -2650,7 +3154,7 @@
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -2662,7 +3166,7 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -2672,38 +3176,38 @@
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -2715,7 +3219,7 @@
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -2725,9 +3229,9 @@
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -2737,31 +3241,50 @@
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
+    <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="s">
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
         <v>50</v>
       </c>
+    </row>
+    <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -2771,9 +3294,9 @@
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -2783,9 +3306,9 @@
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
     </row>
-    <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -2795,50 +3318,31 @@
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-    </row>
-    <row r="54" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
+    </row>
+    <row r="52" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -2848,11 +3352,99 @@
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
     </row>
+    <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+    </row>
+    <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+    </row>
+    <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="29">
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A30:H30"/>
@@ -2860,19 +3452,26 @@
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="A33:H33"/>
     <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="A40:H40"/>
     <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A47:H47"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A64:H64"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2915,17 +3514,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -2934,14 +3533,14 @@
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
       <c r="H4" s="16" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="I4" s="16"/>
       <c r="J4" s="16"/>
       <c r="K4" s="16"/>
       <c r="L4" s="16"/>
       <c r="M4" s="16" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="N4" s="16"/>
       <c r="O4" s="16"/>
@@ -2953,7 +3552,7 @@
       <c r="U4" s="16"/>
       <c r="V4" s="16"/>
       <c r="W4" s="16" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="X4" s="16"/>
       <c r="Y4" s="16"/>
@@ -2961,14 +3560,14 @@
       <c r="AA4" s="16"/>
       <c r="AB4" s="16"/>
       <c r="AC4" s="16" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="AD4" s="16"/>
       <c r="AE4" s="16"/>
       <c r="AF4" s="16"/>
       <c r="AG4" s="16"/>
       <c r="AH4" s="16" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="AI4" s="16"/>
       <c r="AJ4" s="16"/>
@@ -2979,12 +3578,12 @@
       <c r="AO4" s="16"/>
       <c r="AP4" s="16"/>
       <c r="AQ4" s="16" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="AR4" s="16"/>
       <c r="AS4" s="16"/>
       <c r="AT4" s="16" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="AU4" s="16"/>
       <c r="AV4" s="16"/>
@@ -2993,85 +3592,85 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="N5" s="5" t="s">
         <v>13</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>14</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="U5" s="5" t="s">
         <v>21</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="W5" s="5" t="s">
         <v>13</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="Y5" s="5" t="s">
         <v>14</v>
       </c>
       <c r="Z5" s="5" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="AB5" s="5" t="s">
         <v>21</v>
@@ -3080,93 +3679,93 @@
         <v>13</v>
       </c>
       <c r="AD5" s="5" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AE5" s="5" t="s">
         <v>14</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AG5" s="5" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="AH5" s="5" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="AI5" s="5" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="AJ5" s="5" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="AK5" s="5" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="AM5" s="5" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="AN5" s="5" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="AO5" s="5" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="AP5" s="5" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="AQ5" s="5" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="AR5" s="5" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="AS5" s="5" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="AT5" s="5" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="AU5" s="5" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="AV5" s="5" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="AW5" s="17" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="AX5" s="17" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>30.09</v>
@@ -3285,7 +3884,7 @@
         <v>Under 2%: pause</v>
       </c>
       <c r="AR6" s="8" t="str">
-        <f aca="false">IF(O6=0,"",IF(Q6=0,"Spend, no sales",IF(U6&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O6=0,"",IF(Q6=0,"Spend, no sales",IF(U6&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Above 3x break-even</v>
       </c>
       <c r="AS6" s="8" t="str">
@@ -3293,41 +3892,41 @@
         <v>Above +300% cap</v>
       </c>
       <c r="AT6" s="19" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="AU6" s="19" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="AV6" s="8" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AW6" s="22"/>
       <c r="AX6" s="22"/>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B7" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>108</v>
-      </c>
       <c r="E7" s="8" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G7" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>121</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>112</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>13.04</v>
@@ -3444,7 +4043,7 @@
         <v>Under 2%: pause</v>
       </c>
       <c r="AR7" s="8" t="str">
-        <f aca="false">IF(O7=0,"",IF(Q7=0,"Spend, no sales",IF(U7&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O7=0,"",IF(Q7=0,"Spend, no sales",IF(U7&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Above 3x break-even</v>
       </c>
       <c r="AS7" s="8" t="str">
@@ -3452,10 +4051,10 @@
         <v>OK</v>
       </c>
       <c r="AT7" s="19" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="AU7" s="19" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="AV7" s="8" t="s">
         <v>124</v>
@@ -3465,28 +4064,28 @@
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>40</v>
@@ -3601,7 +4200,7 @@
         <v>Under 2%: pause</v>
       </c>
       <c r="AR8" s="8" t="str">
-        <f aca="false">IF(O8=0,"",IF(Q8=0,"Spend, no sales",IF(U8&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O8=0,"",IF(Q8=0,"Spend, no sales",IF(U8&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Above 3x break-even</v>
       </c>
       <c r="AS8" s="8" t="str">
@@ -3609,41 +4208,41 @@
         <v/>
       </c>
       <c r="AT8" s="19" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="AU8" s="19" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="AV8" s="8" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AW8" s="22"/>
       <c r="AX8" s="22"/>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>9.41</v>
@@ -3762,7 +4361,7 @@
         <v>2% to 4%: hold at lower bid</v>
       </c>
       <c r="AR9" s="8" t="str">
-        <f aca="false">IF(O9=0,"",IF(Q9=0,"Spend, no sales",IF(U9&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O9=0,"",IF(Q9=0,"Spend, no sales",IF(U9&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Above 3x break-even</v>
       </c>
       <c r="AS9" s="8" t="str">
@@ -3770,10 +4369,10 @@
         <v>OK</v>
       </c>
       <c r="AT9" s="19" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="AU9" s="19" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="AV9" s="8" t="s">
         <v>124</v>
@@ -3783,28 +4382,28 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>4.5</v>
@@ -3921,7 +4520,7 @@
         <v>Under 100 clicks: watch</v>
       </c>
       <c r="AR10" s="8" t="str">
-        <f aca="false">IF(O10=0,"",IF(Q10=0,"Spend, no sales",IF(U10&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O10=0,"",IF(Q10=0,"Spend, no sales",IF(U10&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Above 3x break-even</v>
       </c>
       <c r="AS10" s="8" t="str">
@@ -3929,10 +4528,10 @@
         <v>OK</v>
       </c>
       <c r="AT10" s="19" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="AU10" s="19" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="AV10" s="8" t="s">
         <v>124</v>
@@ -3942,28 +4541,28 @@
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>5.72</v>
@@ -4078,7 +4677,7 @@
         <v>2% to 4%: hold at lower bid</v>
       </c>
       <c r="AR11" s="8" t="str">
-        <f aca="false">IF(O11=0,"",IF(Q11=0,"Spend, no sales",IF(U11&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O11=0,"",IF(Q11=0,"Spend, no sales",IF(U11&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Above 3x break-even</v>
       </c>
       <c r="AS11" s="8" t="str">
@@ -4086,41 +4685,41 @@
         <v/>
       </c>
       <c r="AT11" s="19" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="AU11" s="19" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="AV11" s="8" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AW11" s="22"/>
       <c r="AX11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>6.59</v>
@@ -4235,7 +4834,7 @@
         <v>20+ clicks, 0 orders: negate / pause</v>
       </c>
       <c r="AR12" s="8" t="str">
-        <f aca="false">IF(O12=0,"",IF(Q12=0,"Spend, no sales",IF(U12&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O12=0,"",IF(Q12=0,"Spend, no sales",IF(U12&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS12" s="8" t="str">
@@ -4243,41 +4842,41 @@
         <v/>
       </c>
       <c r="AT12" s="19" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="AU12" s="19" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="AV12" s="8" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AW12" s="22"/>
       <c r="AX12" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>47.56</v>
@@ -4392,7 +4991,7 @@
         <v>Under 100 clicks: watch</v>
       </c>
       <c r="AR13" s="8" t="str">
-        <f aca="false">IF(O13=0,"",IF(Q13=0,"Spend, no sales",IF(U13&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O13=0,"",IF(Q13=0,"Spend, no sales",IF(U13&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Above 3x break-even</v>
       </c>
       <c r="AS13" s="8" t="str">
@@ -4400,41 +4999,41 @@
         <v/>
       </c>
       <c r="AT13" s="19" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="AU13" s="19" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AV13" s="8" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="AW13" s="22"/>
       <c r="AX13" s="22"/>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>7.56</v>
@@ -4549,7 +5148,7 @@
         <v>20+ clicks, 0 orders: negate / pause</v>
       </c>
       <c r="AR14" s="8" t="str">
-        <f aca="false">IF(O14=0,"",IF(Q14=0,"Spend, no sales",IF(U14&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O14=0,"",IF(Q14=0,"Spend, no sales",IF(U14&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS14" s="8" t="str">
@@ -4557,41 +5156,41 @@
         <v/>
       </c>
       <c r="AT14" s="19" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AU14" s="19" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="AV14" s="8" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="AW14" s="22"/>
       <c r="AX14" s="22"/>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>5.66</v>
@@ -4708,7 +5307,7 @@
         <v>2% to 4%: hold at lower bid</v>
       </c>
       <c r="AR15" s="8" t="str">
-        <f aca="false">IF(O15=0,"",IF(Q15=0,"Spend, no sales",IF(U15&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O15=0,"",IF(Q15=0,"Spend, no sales",IF(U15&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Above 3x break-even</v>
       </c>
       <c r="AS15" s="8" t="str">
@@ -4716,41 +5315,41 @@
         <v>Above +300% cap</v>
       </c>
       <c r="AT15" s="19" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="AU15" s="19" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="AV15" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW15" s="22"/>
       <c r="AX15" s="22"/>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>6.38</v>
@@ -4865,7 +5464,7 @@
         <v>Under 100 clicks: watch</v>
       </c>
       <c r="AR16" s="8" t="str">
-        <f aca="false">IF(O16=0,"",IF(Q16=0,"Spend, no sales",IF(U16&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O16=0,"",IF(Q16=0,"Spend, no sales",IF(U16&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Above 3x break-even</v>
       </c>
       <c r="AS16" s="8" t="str">
@@ -4873,41 +5472,41 @@
         <v/>
       </c>
       <c r="AT16" s="19" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="AU16" s="19" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="AV16" s="8" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AW16" s="22"/>
       <c r="AX16" s="22"/>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>30</v>
@@ -5022,7 +5621,7 @@
         <v>20+ clicks, 0 orders: negate / pause</v>
       </c>
       <c r="AR17" s="8" t="str">
-        <f aca="false">IF(O17=0,"",IF(Q17=0,"Spend, no sales",IF(U17&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O17=0,"",IF(Q17=0,"Spend, no sales",IF(U17&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS17" s="8" t="str">
@@ -5030,41 +5629,41 @@
         <v/>
       </c>
       <c r="AT17" s="19" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="AU17" s="19" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="AV17" s="8" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AW17" s="22"/>
       <c r="AX17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>7.11</v>
@@ -5179,7 +5778,7 @@
         <v>Under 100 clicks: watch</v>
       </c>
       <c r="AR18" s="8" t="str">
-        <f aca="false">IF(O18=0,"",IF(Q18=0,"Spend, no sales",IF(U18&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O18=0,"",IF(Q18=0,"Spend, no sales",IF(U18&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Above 3x break-even</v>
       </c>
       <c r="AS18" s="8" t="str">
@@ -5187,41 +5786,41 @@
         <v/>
       </c>
       <c r="AT18" s="19" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="AU18" s="19" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="AV18" s="8" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="AW18" s="22"/>
       <c r="AX18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>49.63</v>
@@ -5336,7 +5935,7 @@
         <v>Under 100 clicks: watch</v>
       </c>
       <c r="AR19" s="8" t="str">
-        <f aca="false">IF(O19=0,"",IF(Q19=0,"Spend, no sales",IF(U19&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O19=0,"",IF(Q19=0,"Spend, no sales",IF(U19&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Above 3x break-even</v>
       </c>
       <c r="AS19" s="8" t="str">
@@ -5344,41 +5943,41 @@
         <v/>
       </c>
       <c r="AT19" s="19" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="AU19" s="19" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="AV19" s="8" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="AW19" s="22"/>
       <c r="AX19" s="22"/>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>5.66</v>
@@ -5495,7 +6094,7 @@
         <v>20+ clicks, 0 orders: negate / pause</v>
       </c>
       <c r="AR20" s="8" t="str">
-        <f aca="false">IF(O20=0,"",IF(Q20=0,"Spend, no sales",IF(U20&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O20=0,"",IF(Q20=0,"Spend, no sales",IF(U20&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS20" s="8" t="str">
@@ -5503,41 +6102,41 @@
         <v>OK</v>
       </c>
       <c r="AT20" s="19" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="AU20" s="19" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="AV20" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW20" s="22"/>
       <c r="AX20" s="22"/>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>12.14</v>
@@ -5654,7 +6253,7 @@
         <v>Under 20 clicks: too early</v>
       </c>
       <c r="AR21" s="8" t="str">
-        <f aca="false">IF(O21=0,"",IF(Q21=0,"Spend, no sales",IF(U21&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O21=0,"",IF(Q21=0,"Spend, no sales",IF(U21&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS21" s="8" t="str">
@@ -5662,41 +6261,41 @@
         <v>Above +300% cap</v>
       </c>
       <c r="AT21" s="19" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="AU21" s="19" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AV21" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW21" s="22"/>
       <c r="AX21" s="22"/>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>5.66</v>
@@ -5811,7 +6410,7 @@
         <v>20+ clicks, 0 orders: negate / pause</v>
       </c>
       <c r="AR22" s="8" t="str">
-        <f aca="false">IF(O22=0,"",IF(Q22=0,"Spend, no sales",IF(U22&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O22=0,"",IF(Q22=0,"Spend, no sales",IF(U22&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS22" s="8" t="str">
@@ -5819,41 +6418,41 @@
         <v/>
       </c>
       <c r="AT22" s="19" t="s">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="AU22" s="19" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="AV22" s="8" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="AW22" s="22"/>
       <c r="AX22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>7.64</v>
@@ -5968,7 +6567,7 @@
         <v>20+ clicks, 0 orders: negate / pause</v>
       </c>
       <c r="AR23" s="8" t="str">
-        <f aca="false">IF(O23=0,"",IF(Q23=0,"Spend, no sales",IF(U23&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O23=0,"",IF(Q23=0,"Spend, no sales",IF(U23&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS23" s="8" t="str">
@@ -5976,41 +6575,41 @@
         <v/>
       </c>
       <c r="AT23" s="19" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AU23" s="19" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AV23" s="8" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="AW23" s="22"/>
       <c r="AX23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>9.34</v>
@@ -6125,7 +6724,7 @@
         <v>20+ clicks, 0 orders: negate / pause</v>
       </c>
       <c r="AR24" s="8" t="str">
-        <f aca="false">IF(O24=0,"",IF(Q24=0,"Spend, no sales",IF(U24&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O24=0,"",IF(Q24=0,"Spend, no sales",IF(U24&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS24" s="8" t="str">
@@ -6133,41 +6732,41 @@
         <v/>
       </c>
       <c r="AT24" s="19" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AU24" s="19" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="AV24" s="8" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="AW24" s="22"/>
       <c r="AX24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>4.5</v>
@@ -6284,7 +6883,7 @@
         <v>20+ clicks, 0 orders: negate / pause</v>
       </c>
       <c r="AR25" s="8" t="str">
-        <f aca="false">IF(O25=0,"",IF(Q25=0,"Spend, no sales",IF(U25&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O25=0,"",IF(Q25=0,"Spend, no sales",IF(U25&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS25" s="8" t="str">
@@ -6292,41 +6891,41 @@
         <v>OK</v>
       </c>
       <c r="AT25" s="19" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="AU25" s="19" t="s">
-        <v>146</v>
+        <v>228</v>
       </c>
       <c r="AV25" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW25" s="22"/>
       <c r="AX25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>40.83</v>
@@ -6441,7 +7040,7 @@
         <v>20+ clicks, 0 orders: negate / pause</v>
       </c>
       <c r="AR26" s="8" t="str">
-        <f aca="false">IF(O26=0,"",IF(Q26=0,"Spend, no sales",IF(U26&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O26=0,"",IF(Q26=0,"Spend, no sales",IF(U26&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS26" s="8" t="str">
@@ -6449,41 +7048,41 @@
         <v/>
       </c>
       <c r="AT26" s="19" t="s">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="AU26" s="19" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="AV26" s="8" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="AW26" s="22"/>
       <c r="AX26" s="22"/>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>8.7</v>
@@ -6598,7 +7197,7 @@
         <v>Under 20 clicks: too early</v>
       </c>
       <c r="AR27" s="8" t="str">
-        <f aca="false">IF(O27=0,"",IF(Q27=0,"Spend, no sales",IF(U27&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O27=0,"",IF(Q27=0,"Spend, no sales",IF(U27&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS27" s="8" t="str">
@@ -6606,41 +7205,41 @@
         <v/>
       </c>
       <c r="AT27" s="19" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AU27" s="19" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="AV27" s="8" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="AW27" s="22"/>
       <c r="AX27" s="22"/>
     </row>
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>19.95</v>
@@ -6757,7 +7356,7 @@
         <v>Under 20 clicks: too early</v>
       </c>
       <c r="AR28" s="8" t="str">
-        <f aca="false">IF(O28=0,"",IF(Q28=0,"Spend, no sales",IF(U28&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O28=0,"",IF(Q28=0,"Spend, no sales",IF(U28&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS28" s="8" t="str">
@@ -6765,41 +7364,41 @@
         <v>Above +300% cap</v>
       </c>
       <c r="AT28" s="19" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="AU28" s="19" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="AV28" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW28" s="22"/>
       <c r="AX28" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>11.21</v>
@@ -6914,7 +7513,7 @@
         <v>20+ clicks, 0 orders: negate / pause</v>
       </c>
       <c r="AR29" s="8" t="str">
-        <f aca="false">IF(O29=0,"",IF(Q29=0,"Spend, no sales",IF(U29&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O29=0,"",IF(Q29=0,"Spend, no sales",IF(U29&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS29" s="8" t="str">
@@ -6922,41 +7521,41 @@
         <v/>
       </c>
       <c r="AT29" s="19" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AU29" s="19" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="AV29" s="8" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="AW29" s="22"/>
       <c r="AX29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G30" s="19" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>4.5</v>
@@ -7071,7 +7670,7 @@
         <v>20+ clicks, 0 orders: negate / pause</v>
       </c>
       <c r="AR30" s="8" t="str">
-        <f aca="false">IF(O30=0,"",IF(Q30=0,"Spend, no sales",IF(U30&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O30=0,"",IF(Q30=0,"Spend, no sales",IF(U30&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS30" s="8" t="str">
@@ -7079,41 +7678,41 @@
         <v/>
       </c>
       <c r="AT30" s="19" t="s">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="AU30" s="19" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="AV30" s="8" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="AW30" s="22"/>
       <c r="AX30" s="22"/>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>4.5</v>
@@ -7230,7 +7829,7 @@
         <v>20+ clicks, 0 orders: negate / pause</v>
       </c>
       <c r="AR31" s="8" t="str">
-        <f aca="false">IF(O31=0,"",IF(Q31=0,"Spend, no sales",IF(U31&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O31=0,"",IF(Q31=0,"Spend, no sales",IF(U31&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS31" s="8" t="str">
@@ -7238,41 +7837,41 @@
         <v>OK</v>
       </c>
       <c r="AT31" s="19" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="AU31" s="19" t="s">
-        <v>146</v>
+        <v>228</v>
       </c>
       <c r="AV31" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW31" s="22"/>
       <c r="AX31" s="22"/>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>4.5</v>
@@ -7387,7 +7986,7 @@
         <v>20+ clicks, 0 orders: negate / pause</v>
       </c>
       <c r="AR32" s="8" t="str">
-        <f aca="false">IF(O32=0,"",IF(Q32=0,"Spend, no sales",IF(U32&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O32=0,"",IF(Q32=0,"Spend, no sales",IF(U32&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS32" s="8" t="str">
@@ -7395,41 +7994,41 @@
         <v/>
       </c>
       <c r="AT32" s="19" t="s">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="AU32" s="19" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="AV32" s="8" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="AW32" s="22"/>
       <c r="AX32" s="22"/>
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="18" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>8.6</v>
@@ -7546,7 +8145,7 @@
         <v>Under 20 clicks: too early</v>
       </c>
       <c r="AR33" s="8" t="str">
-        <f aca="false">IF(O33=0,"",IF(Q33=0,"Spend, no sales",IF(U33&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O33=0,"",IF(Q33=0,"Spend, no sales",IF(U33&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS33" s="8" t="str">
@@ -7554,41 +8153,41 @@
         <v>Above +300% cap</v>
       </c>
       <c r="AT33" s="19" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="AU33" s="19" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="AV33" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW33" s="22"/>
       <c r="AX33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I34" s="7" t="n">
         <v>5.66</v>
@@ -7705,7 +8304,7 @@
         <v>Under 20 clicks: too early</v>
       </c>
       <c r="AR34" s="8" t="str">
-        <f aca="false">IF(O34=0,"",IF(Q34=0,"Spend, no sales",IF(U34&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O34=0,"",IF(Q34=0,"Spend, no sales",IF(U34&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS34" s="8" t="str">
@@ -7713,41 +8312,41 @@
         <v>OK</v>
       </c>
       <c r="AT34" s="19" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="AU34" s="19" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="AV34" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW34" s="22"/>
       <c r="AX34" s="22"/>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="18" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="G35" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="H35" s="8" t="s">
         <v>121</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>112</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>13.97</v>
@@ -7864,7 +8463,7 @@
         <v>Under 20 clicks: too early</v>
       </c>
       <c r="AR35" s="8" t="str">
-        <f aca="false">IF(O35=0,"",IF(Q35=0,"Spend, no sales",IF(U35&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O35=0,"",IF(Q35=0,"Spend, no sales",IF(U35&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Within 3x break-even</v>
       </c>
       <c r="AS35" s="8" t="str">
@@ -7872,10 +8471,10 @@
         <v>OK</v>
       </c>
       <c r="AT35" s="19" t="s">
-        <v>259</v>
+        <v>144</v>
       </c>
       <c r="AU35" s="19" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AV35" s="8" t="s">
         <v>124</v>
@@ -7885,28 +8484,28 @@
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="18" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G36" s="19" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I36" s="7" t="n">
         <v>4.5</v>
@@ -8021,7 +8620,7 @@
         <v>Under 20 clicks: too early</v>
       </c>
       <c r="AR36" s="8" t="str">
-        <f aca="false">IF(O36=0,"",IF(Q36=0,"Spend, no sales",IF(U36&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O36=0,"",IF(Q36=0,"Spend, no sales",IF(U36&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS36" s="8" t="str">
@@ -8029,41 +8628,41 @@
         <v/>
       </c>
       <c r="AT36" s="19" t="s">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="AU36" s="19" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="AV36" s="8" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="AW36" s="22"/>
       <c r="AX36" s="22"/>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G37" s="19" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I37" s="7" t="n">
         <v>4.5</v>
@@ -8180,7 +8779,7 @@
         <v>Under 20 clicks: too early</v>
       </c>
       <c r="AR37" s="8" t="str">
-        <f aca="false">IF(O37=0,"",IF(Q37=0,"Spend, no sales",IF(U37&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O37=0,"",IF(Q37=0,"Spend, no sales",IF(U37&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS37" s="8" t="str">
@@ -8188,41 +8787,41 @@
         <v>OK</v>
       </c>
       <c r="AT37" s="19" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="AU37" s="19" t="s">
-        <v>146</v>
+        <v>228</v>
       </c>
       <c r="AV37" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW37" s="22"/>
       <c r="AX37" s="22"/>
     </row>
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="18" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G38" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="H38" s="8" t="s">
         <v>121</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>112</v>
       </c>
       <c r="I38" s="7" t="n">
         <v>8.7</v>
@@ -8339,7 +8938,7 @@
         <v>Under 20 clicks: too early</v>
       </c>
       <c r="AR38" s="8" t="str">
-        <f aca="false">IF(O38=0,"",IF(Q38=0,"Spend, no sales",IF(U38&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O38=0,"",IF(Q38=0,"Spend, no sales",IF(U38&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS38" s="8" t="str">
@@ -8347,41 +8946,41 @@
         <v>Above +300% cap</v>
       </c>
       <c r="AT38" s="19" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="AU38" s="19" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AV38" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW38" s="22"/>
       <c r="AX38" s="22"/>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="18" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G39" s="19" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I39" s="7" t="n">
         <v>4.5</v>
@@ -8498,7 +9097,7 @@
         <v>Under 20 clicks: too early</v>
       </c>
       <c r="AR39" s="8" t="str">
-        <f aca="false">IF(O39=0,"",IF(Q39=0,"Spend, no sales",IF(U39&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O39=0,"",IF(Q39=0,"Spend, no sales",IF(U39&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS39" s="8" t="str">
@@ -8506,41 +9105,41 @@
         <v>OK</v>
       </c>
       <c r="AT39" s="19" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="AU39" s="19" t="s">
-        <v>146</v>
+        <v>228</v>
       </c>
       <c r="AV39" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW39" s="22"/>
       <c r="AX39" s="22"/>
     </row>
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I40" s="7" t="n">
         <v>8.83</v>
@@ -8657,7 +9256,7 @@
         <v>Under 20 clicks: too early</v>
       </c>
       <c r="AR40" s="8" t="str">
-        <f aca="false">IF(O40=0,"",IF(Q40=0,"Spend, no sales",IF(U40&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O40=0,"",IF(Q40=0,"Spend, no sales",IF(U40&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS40" s="8" t="str">
@@ -8665,41 +9264,41 @@
         <v>Above +300% cap</v>
       </c>
       <c r="AT40" s="19" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="AU40" s="19" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="AV40" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW40" s="22"/>
       <c r="AX40" s="22"/>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I41" s="7" t="n">
         <v>4.5</v>
@@ -8816,7 +9415,7 @@
         <v>Under 20 clicks: too early</v>
       </c>
       <c r="AR41" s="8" t="str">
-        <f aca="false">IF(O41=0,"",IF(Q41=0,"Spend, no sales",IF(U41&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O41=0,"",IF(Q41=0,"Spend, no sales",IF(U41&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS41" s="8" t="str">
@@ -8824,41 +9423,41 @@
         <v>OK</v>
       </c>
       <c r="AT41" s="19" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="AU41" s="19" t="s">
-        <v>146</v>
+        <v>228</v>
       </c>
       <c r="AV41" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW41" s="22"/>
       <c r="AX41" s="22"/>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="18" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G42" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="H42" s="8" t="s">
         <v>121</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>112</v>
       </c>
       <c r="I42" s="7" t="n">
         <v>19.76</v>
@@ -8975,7 +9574,7 @@
         <v>Under 20 clicks: too early</v>
       </c>
       <c r="AR42" s="8" t="str">
-        <f aca="false">IF(O42=0,"",IF(Q42=0,"Spend, no sales",IF(U42&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O42=0,"",IF(Q42=0,"Spend, no sales",IF(U42&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS42" s="8" t="str">
@@ -8983,41 +9582,41 @@
         <v>Above +300% cap</v>
       </c>
       <c r="AT42" s="19" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="AU42" s="19" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="AV42" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW42" s="22"/>
       <c r="AX42" s="22"/>
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I43" s="7" t="n">
         <v>11.32</v>
@@ -9134,7 +9733,7 @@
         <v>Under 20 clicks: too early</v>
       </c>
       <c r="AR43" s="8" t="str">
-        <f aca="false">IF(O43=0,"",IF(Q43=0,"Spend, no sales",IF(U43&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O43=0,"",IF(Q43=0,"Spend, no sales",IF(U43&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS43" s="8" t="str">
@@ -9142,41 +9741,41 @@
         <v>Above +300% cap</v>
       </c>
       <c r="AT43" s="19" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="AU43" s="19" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AV43" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW43" s="22"/>
       <c r="AX43" s="22"/>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="18" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I44" s="7" t="n">
         <v>4.5</v>
@@ -9293,7 +9892,7 @@
         <v>Under 20 clicks: too early</v>
       </c>
       <c r="AR44" s="8" t="str">
-        <f aca="false">IF(O44=0,"",IF(Q44=0,"Spend, no sales",IF(U44&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O44=0,"",IF(Q44=0,"Spend, no sales",IF(U44&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS44" s="8" t="str">
@@ -9301,41 +9900,41 @@
         <v>OK</v>
       </c>
       <c r="AT44" s="19" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="AU44" s="19" t="s">
-        <v>146</v>
+        <v>228</v>
       </c>
       <c r="AV44" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW44" s="22"/>
       <c r="AX44" s="22"/>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="18" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G45" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="H45" s="8" t="s">
         <v>121</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>112</v>
       </c>
       <c r="I45" s="7" t="n">
         <v>6.59</v>
@@ -9452,7 +10051,7 @@
         <v>Under 20 clicks: too early</v>
       </c>
       <c r="AR45" s="8" t="str">
-        <f aca="false">IF(O45=0,"",IF(Q45=0,"Spend, no sales",IF(U45&gt;Rules!$B$24,"Above 3x break-even","Within 3x break-even")))</f>
+        <f aca="false">IF(O45=0,"",IF(Q45=0,"Spend, no sales",IF(U45&gt;Rules!$B$32,"Above 3x break-even","Within 3x break-even")))</f>
         <v>Spend, no sales</v>
       </c>
       <c r="AS45" s="8" t="str">
@@ -9460,20 +10059,20 @@
         <v>Above +300% cap</v>
       </c>
       <c r="AT45" s="19" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="AU45" s="19" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="AV45" s="8" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="AW45" s="22"/>
       <c r="AX45" s="22"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="23" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="B46" s="23"/>
       <c r="C46" s="23"/>
@@ -9632,7 +10231,7 @@
   </mergeCells>
   <conditionalFormatting sqref="AT6:AT45">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
-      <formula>LEFT($AT6,9)="Pause now"</formula>
+      <formula>LEFT($AT6,5)="Pause"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>LEFT($AT6,6)="Joseph"</formula>
@@ -9666,6 +10265,2292 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF70AD47"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:AI35"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="18" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="14" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="W4" s="16"/>
+      <c r="X4" s="16"/>
+      <c r="Y4" s="16"/>
+      <c r="Z4" s="16"/>
+      <c r="AA4" s="16"/>
+      <c r="AB4" s="16"/>
+      <c r="AC4" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="AD4" s="16"/>
+      <c r="AE4" s="16"/>
+      <c r="AF4" s="16"/>
+      <c r="AG4" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="AH4" s="16"/>
+      <c r="AI4" s="16"/>
+    </row>
+    <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="AA5" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="AB5" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="AC5" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="AD5" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="AE5" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="AF5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG5" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="AH5" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="AI5" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="C6" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$E$6:$E$45,MATCH($A6,Campaigns!$A$6:$A$45,0))</f>
+        <v>Brand defence</v>
+      </c>
+      <c r="D6" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($A6,Campaigns!$A$6:$A$45,0))</f>
+        <v>ENABLED</v>
+      </c>
+      <c r="E6" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$G$6:$G$45,MATCH($A6,Campaigns!$A$6:$A$45,0))</f>
+        <v>Phase 0: run</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$AH$6:$AH$45,MATCH($A6,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AJ$6:$AJ$45,MATCH($A6,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AL$6:$AL$45,MATCH($A6,Campaigns!$A$6:$A$45,0))</f>
+        <v>4</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$AI$6:$AI$45,MATCH($A6,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AK$6:$AK$45,MATCH($A6,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AM$6:$AM$45,MATCH($A6,Campaigns!$A$6:$A$45,0))</f>
+        <v>1.38</v>
+      </c>
+      <c r="I6" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($A6,Campaigns!$A$6:$A$45,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$Q$6:$Q$45,MATCH($A6,Campaigns!$A$6:$A$45,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$Y$6:$Y$45,MATCH($A6,Campaigns!$A$6:$A$45,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <f aca="false">IF(I6=0,AVERAGE(Rules!$B$15,Rules!$B$16),J6/I6)</f>
+        <v>30.99</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <f aca="false">IF(F6=0,0,G6/F6)</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="10" t="n">
+        <f aca="false">(G6+Rules!$B$37*Rules!$B$20)/(F6+Rules!$B$20)</f>
+        <v>0.0118708452041785</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <f aca="false">IF(F6=0,0,H6/F6)</f>
+        <v>0.345</v>
+      </c>
+      <c r="P6" s="10" t="str">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($A6,Campaigns!$A$6:$A$45,0))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="19" t="str">
+        <f aca="false">IF(C6="Brand defence","Brand defence: keep on",IF(G6=0,"No on-Amazon orders: pause",IF(K6&gt;0,IF(D6="ENABLED","Converting now: keep, optimize","Converting now: re-enable, optimize"),IF(D6="ENABLED","Converted before: keep, optimize","Converted before: re-enable, optimize"))))</f>
+        <v>Brand defence: keep on</v>
+      </c>
+      <c r="R6" s="7" t="n">
+        <f aca="false">Rules!$B$19*L6*N6</f>
+        <v>0.139793447293447</v>
+      </c>
+      <c r="S6" s="7" t="n">
+        <f aca="false">MAX(Rules!$B$24,R6*Rules!$B$39)</f>
+        <v>0.1</v>
+      </c>
+      <c r="T6" s="7" t="n">
+        <f aca="false">R6*Rules!$B$38</f>
+        <v>0.279586894586895</v>
+      </c>
+      <c r="U6" s="20" t="n">
+        <f aca="false">Rules!$B$9</f>
+        <v>3</v>
+      </c>
+      <c r="V6" s="7" t="n">
+        <f aca="false">IF(O6=0,Rules!$B$7,O6)</f>
+        <v>0.345</v>
+      </c>
+      <c r="W6" s="10" t="n">
+        <f aca="false">IF(V6=0,0,S6/V6-1)</f>
+        <v>-0.710144927536232</v>
+      </c>
+      <c r="X6" s="7" t="n">
+        <f aca="false">V6</f>
+        <v>0.345</v>
+      </c>
+      <c r="Y6" s="10" t="n">
+        <f aca="false">IF(V6=0,0,X6/V6-1)</f>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA6" s="20" t="n">
+        <f aca="false">IF(Z6="",U6,Z6+MAX(MIN(U6-Z6,Rules!$B$23),-Rules!$B$23))</f>
+        <v>3.6</v>
+      </c>
+      <c r="AB6" s="7" t="n">
+        <f aca="false">X6*(1+AA6)</f>
+        <v>1.587</v>
+      </c>
+      <c r="AC6" s="32" t="n">
+        <f aca="false">F6/Rules!$B$26*7</f>
+        <v>0.482758620689655</v>
+      </c>
+      <c r="AD6" s="7" t="n">
+        <f aca="false">IF(LEFT(Q6,2)="No",0,AC6*O6*(1+Y6))</f>
+        <v>0.166551724137931</v>
+      </c>
+      <c r="AE6" s="21" t="n">
+        <f aca="false">IF(LEFT(Q6,2)="No",0,AC6*N6)</f>
+        <v>0.00573075285718964</v>
+      </c>
+      <c r="AF6" s="10" t="n">
+        <f aca="false">IF(OR(AE6=0,L6=0),"",AD6/(AE6*L6))</f>
+        <v>0.937812197483059</v>
+      </c>
+      <c r="AG6" s="8" t="str">
+        <f aca="false">IF(OR(LEFT(Q6,2)="No",D6="PAUSED",ABS(Y6)&gt;Rules!$B$25,AA6&lt;&gt;Z6),"Joseph","Shayan")</f>
+        <v>Joseph</v>
+      </c>
+      <c r="AH6" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI6" s="22"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$E$6:$E$45,MATCH($A7,Campaigns!$A$6:$A$45,0))</f>
+        <v>Boho core</v>
+      </c>
+      <c r="D7" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($A7,Campaigns!$A$6:$A$45,0))</f>
+        <v>ENABLED</v>
+      </c>
+      <c r="E7" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$G$6:$G$45,MATCH($A7,Campaigns!$A$6:$A$45,0))</f>
+        <v>Phase 0: run</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$AH$6:$AH$45,MATCH($A7,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AJ$6:$AJ$45,MATCH($A7,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AL$6:$AL$45,MATCH($A7,Campaigns!$A$6:$A$45,0))</f>
+        <v>184</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$AI$6:$AI$45,MATCH($A7,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AK$6:$AK$45,MATCH($A7,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AM$6:$AM$45,MATCH($A7,Campaigns!$A$6:$A$45,0))</f>
+        <v>128.41</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($A7,Campaigns!$A$6:$A$45,0))</f>
+        <v>4</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$Q$6:$Q$45,MATCH($A7,Campaigns!$A$6:$A$45,0))</f>
+        <v>150.95</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$Y$6:$Y$45,MATCH($A7,Campaigns!$A$6:$A$45,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <f aca="false">IF(I7=0,AVERAGE(Rules!$B$15,Rules!$B$16),J7/I7)</f>
+        <v>37.7375</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <f aca="false">IF(F7=0,0,G7/F7)</f>
+        <v>0.0217391304347826</v>
+      </c>
+      <c r="N7" s="10" t="n">
+        <f aca="false">(G7+Rules!$B$37*Rules!$B$20)/(F7+Rules!$B$20)</f>
+        <v>0.019833442910366</v>
+      </c>
+      <c r="O7" s="7" t="n">
+        <f aca="false">IF(F7=0,0,H7/F7)</f>
+        <v>0.697880434782609</v>
+      </c>
+      <c r="P7" s="10" t="n">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($A7,Campaigns!$A$6:$A$45,0))</f>
+        <v>0.850679032792315</v>
+      </c>
+      <c r="Q7" s="19" t="str">
+        <f aca="false">IF(C7="Brand defence","Brand defence: keep on",IF(G7=0,"No on-Amazon orders: pause",IF(K7&gt;0,IF(D7="ENABLED","Converting now: keep, optimize","Converting now: re-enable, optimize"),IF(D7="ENABLED","Converted before: keep, optimize","Converted before: re-enable, optimize"))))</f>
+        <v>Converting now: keep, optimize</v>
+      </c>
+      <c r="R7" s="7" t="n">
+        <f aca="false">Rules!$B$19*L7*N7</f>
+        <v>0.284416529695376</v>
+      </c>
+      <c r="S7" s="7" t="n">
+        <f aca="false">MAX(Rules!$B$24,R7*Rules!$B$39)</f>
+        <v>0.144367609433228</v>
+      </c>
+      <c r="T7" s="7" t="n">
+        <f aca="false">R7*Rules!$B$38</f>
+        <v>0.568833059390752</v>
+      </c>
+      <c r="U7" s="20" t="n">
+        <f aca="false">MAX(0,MIN(Rules!$B$9,T7/S7-1))</f>
+        <v>2.94017094017094</v>
+      </c>
+      <c r="V7" s="33" t="n">
+        <f aca="false">0.52</f>
+        <v>0.52</v>
+      </c>
+      <c r="W7" s="10" t="n">
+        <f aca="false">IF(V7=0,0,S7/V7-1)</f>
+        <v>-0.722369981859178</v>
+      </c>
+      <c r="X7" s="7" t="n">
+        <f aca="false">IF(W7&lt;0,MAX(S7,V7*(1-Rules!$B$21)),MIN(S7,V7*(1+Rules!$B$22)))</f>
+        <v>0.39</v>
+      </c>
+      <c r="Y7" s="10" t="n">
+        <f aca="false">IF(V7=0,0,X7/V7-1)</f>
+        <v>-0.25</v>
+      </c>
+      <c r="Z7" s="31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA7" s="20" t="n">
+        <f aca="false">IF(Z7="",U7,Z7+MAX(MIN(U7-Z7,Rules!$B$23),-Rules!$B$23))</f>
+        <v>2.94017094017094</v>
+      </c>
+      <c r="AB7" s="7" t="n">
+        <f aca="false">X7*(1+AA7)</f>
+        <v>1.53666666666667</v>
+      </c>
+      <c r="AC7" s="32" t="n">
+        <f aca="false">F7/Rules!$B$26*7</f>
+        <v>22.2068965517241</v>
+      </c>
+      <c r="AD7" s="7" t="n">
+        <f aca="false">IF(LEFT(Q7,2)="No",0,AC7*O7*(1+Y7))</f>
+        <v>11.6233189655172</v>
+      </c>
+      <c r="AE7" s="21" t="n">
+        <f aca="false">IF(LEFT(Q7,2)="No",0,AC7*N7)</f>
+        <v>0.440439214975024</v>
+      </c>
+      <c r="AF7" s="10" t="n">
+        <f aca="false">IF(OR(AE7=0,L7=0),"",AD7/(AE7*L7))</f>
+        <v>0.699312111451718</v>
+      </c>
+      <c r="AG7" s="8" t="str">
+        <f aca="false">IF(OR(LEFT(Q7,2)="No",D7="PAUSED",ABS(Y7)&gt;Rules!$B$25,AA7&lt;&gt;Z7),"Joseph","Shayan")</f>
+        <v>Joseph</v>
+      </c>
+      <c r="AH7" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI7" s="22"/>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$E$6:$E$45,MATCH($A8,Campaigns!$A$6:$A$45,0))</f>
+        <v>Boho core</v>
+      </c>
+      <c r="D8" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($A8,Campaigns!$A$6:$A$45,0))</f>
+        <v>PAUSED</v>
+      </c>
+      <c r="E8" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$G$6:$G$45,MATCH($A8,Campaigns!$A$6:$A$45,0))</f>
+        <v>Phase 0: run</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$AH$6:$AH$45,MATCH($A8,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AJ$6:$AJ$45,MATCH($A8,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AL$6:$AL$45,MATCH($A8,Campaigns!$A$6:$A$45,0))</f>
+        <v>185</v>
+      </c>
+      <c r="G8" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$AI$6:$AI$45,MATCH($A8,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AK$6:$AK$45,MATCH($A8,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AM$6:$AM$45,MATCH($A8,Campaigns!$A$6:$A$45,0))</f>
+        <v>138.57</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($A8,Campaigns!$A$6:$A$45,0))</f>
+        <v>3</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$Q$6:$Q$45,MATCH($A8,Campaigns!$A$6:$A$45,0))</f>
+        <v>88.97</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$Y$6:$Y$45,MATCH($A8,Campaigns!$A$6:$A$45,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <f aca="false">IF(I8=0,AVERAGE(Rules!$B$15,Rules!$B$16),J8/I8)</f>
+        <v>29.6566666666667</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <f aca="false">IF(F8=0,0,G8/F8)</f>
+        <v>0.0162162162162162</v>
+      </c>
+      <c r="N8" s="10" t="n">
+        <f aca="false">(G8+Rules!$B$37*Rules!$B$20)/(F8+Rules!$B$20)</f>
+        <v>0.015493726132024</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <f aca="false">IF(F8=0,0,H8/F8)</f>
+        <v>0.749027027027027</v>
+      </c>
+      <c r="P8" s="10" t="n">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($A8,Campaigns!$A$6:$A$45,0))</f>
+        <v>1.55737889176127</v>
+      </c>
+      <c r="Q8" s="19" t="str">
+        <f aca="false">IF(C8="Brand defence","Brand defence: keep on",IF(G8=0,"No on-Amazon orders: pause",IF(K8&gt;0,IF(D8="ENABLED","Converting now: keep, optimize","Converting now: re-enable, optimize"),IF(D8="ENABLED","Converted before: keep, optimize","Converted before: re-enable, optimize"))))</f>
+        <v>Converted before: re-enable, optimize</v>
+      </c>
+      <c r="R8" s="7" t="n">
+        <f aca="false">Rules!$B$19*L8*N8</f>
+        <v>0.174607063102382</v>
+      </c>
+      <c r="S8" s="7" t="n">
+        <f aca="false">MAX(Rules!$B$24,R8*Rules!$B$39)</f>
+        <v>0.1</v>
+      </c>
+      <c r="T8" s="7" t="n">
+        <f aca="false">R8*Rules!$B$38</f>
+        <v>0.349214126204765</v>
+      </c>
+      <c r="U8" s="20" t="n">
+        <f aca="false">MAX(0,MIN(Rules!$B$9,T8/S8-1))</f>
+        <v>2.49214126204764</v>
+      </c>
+      <c r="V8" s="7" t="n">
+        <f aca="false">IF(O8=0,Rules!$B$7,O8)</f>
+        <v>0.749027027027027</v>
+      </c>
+      <c r="W8" s="10" t="n">
+        <f aca="false">IF(V8=0,0,S8/V8-1)</f>
+        <v>-0.866493469004835</v>
+      </c>
+      <c r="X8" s="7" t="n">
+        <f aca="false">IF(W8&lt;0,MAX(S8,V8*(1-Rules!$B$21)),MIN(S8,V8*(1+Rules!$B$22)))</f>
+        <v>0.56177027027027</v>
+      </c>
+      <c r="Y8" s="10" t="n">
+        <f aca="false">IF(V8=0,0,X8/V8-1)</f>
+        <v>-0.25</v>
+      </c>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20" t="n">
+        <f aca="false">IF(Z8="",U8,Z8+MAX(MIN(U8-Z8,Rules!$B$23),-Rules!$B$23))</f>
+        <v>2.49214126204764</v>
+      </c>
+      <c r="AB8" s="7" t="n">
+        <f aca="false">X8*(1+AA8)</f>
+        <v>1.96178114060247</v>
+      </c>
+      <c r="AC8" s="32" t="n">
+        <f aca="false">F8/Rules!$B$26*7</f>
+        <v>22.3275862068966</v>
+      </c>
+      <c r="AD8" s="7" t="n">
+        <f aca="false">IF(LEFT(Q8,2)="No",0,AC8*O8*(1+Y8))</f>
+        <v>12.542974137931</v>
+      </c>
+      <c r="AE8" s="21" t="n">
+        <f aca="false">IF(LEFT(Q8,2)="No",0,AC8*N8)</f>
+        <v>0.345937505878812</v>
+      </c>
+      <c r="AF8" s="10" t="n">
+        <f aca="false">IF(OR(AE8=0,L8=0),"",AD8/(AE8*L8))</f>
+        <v>1.22258916054004</v>
+      </c>
+      <c r="AG8" s="8" t="str">
+        <f aca="false">IF(OR(LEFT(Q8,2)="No",D8="PAUSED",ABS(Y8)&gt;Rules!$B$25,AA8&lt;&gt;Z8),"Joseph","Shayan")</f>
+        <v>Joseph</v>
+      </c>
+      <c r="AH8" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI8" s="22"/>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$E$6:$E$45,MATCH($A9,Campaigns!$A$6:$A$45,0))</f>
+        <v>Boho core</v>
+      </c>
+      <c r="D9" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($A9,Campaigns!$A$6:$A$45,0))</f>
+        <v>PAUSED</v>
+      </c>
+      <c r="E9" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$G$6:$G$45,MATCH($A9,Campaigns!$A$6:$A$45,0))</f>
+        <v>Phase 0: run</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$AH$6:$AH$45,MATCH($A9,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AJ$6:$AJ$45,MATCH($A9,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AL$6:$AL$45,MATCH($A9,Campaigns!$A$6:$A$45,0))</f>
+        <v>125</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$AI$6:$AI$45,MATCH($A9,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AK$6:$AK$45,MATCH($A9,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AM$6:$AM$45,MATCH($A9,Campaigns!$A$6:$A$45,0))</f>
+        <v>92.74</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($A9,Campaigns!$A$6:$A$45,0))</f>
+        <v>3</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$Q$6:$Q$45,MATCH($A9,Campaigns!$A$6:$A$45,0))</f>
+        <v>80.97</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$Y$6:$Y$45,MATCH($A9,Campaigns!$A$6:$A$45,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <f aca="false">IF(I9=0,AVERAGE(Rules!$B$15,Rules!$B$16),J9/I9)</f>
+        <v>26.99</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <f aca="false">IF(F9=0,0,G9/F9)</f>
+        <v>0.024</v>
+      </c>
+      <c r="N9" s="10" t="n">
+        <f aca="false">(G9+Rules!$B$37*Rules!$B$20)/(F9+Rules!$B$20)</f>
+        <v>0.0208058608058608</v>
+      </c>
+      <c r="O9" s="7" t="n">
+        <f aca="false">IF(F9=0,0,H9/F9)</f>
+        <v>0.74192</v>
+      </c>
+      <c r="P9" s="10" t="n">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($A9,Campaigns!$A$6:$A$45,0))</f>
+        <v>1.14536247993084</v>
+      </c>
+      <c r="Q9" s="19" t="str">
+        <f aca="false">IF(C9="Brand defence","Brand defence: keep on",IF(G9=0,"No on-Amazon orders: pause",IF(K9&gt;0,IF(D9="ENABLED","Converting now: keep, optimize","Converting now: re-enable, optimize"),IF(D9="ENABLED","Converted before: keep, optimize","Converted before: re-enable, optimize"))))</f>
+        <v>Converted before: re-enable, optimize</v>
+      </c>
+      <c r="R9" s="7" t="n">
+        <f aca="false">Rules!$B$19*L9*N9</f>
+        <v>0.21338906959707</v>
+      </c>
+      <c r="S9" s="7" t="n">
+        <f aca="false">MAX(Rules!$B$24,R9*Rules!$B$39)</f>
+        <v>0.108314625348621</v>
+      </c>
+      <c r="T9" s="7" t="n">
+        <f aca="false">R9*Rules!$B$38</f>
+        <v>0.426778139194139</v>
+      </c>
+      <c r="U9" s="20" t="n">
+        <f aca="false">MAX(0,MIN(Rules!$B$9,T9/S9-1))</f>
+        <v>2.94017094017094</v>
+      </c>
+      <c r="V9" s="7" t="n">
+        <f aca="false">IF(O9=0,Rules!$B$7,O9)</f>
+        <v>0.74192</v>
+      </c>
+      <c r="W9" s="10" t="n">
+        <f aca="false">IF(V9=0,0,S9/V9-1)</f>
+        <v>-0.85400767555987</v>
+      </c>
+      <c r="X9" s="7" t="n">
+        <f aca="false">IF(W9&lt;0,MAX(S9,V9*(1-Rules!$B$21)),MIN(S9,V9*(1+Rules!$B$22)))</f>
+        <v>0.55644</v>
+      </c>
+      <c r="Y9" s="10" t="n">
+        <f aca="false">IF(V9=0,0,X9/V9-1)</f>
+        <v>-0.25</v>
+      </c>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20" t="n">
+        <f aca="false">IF(Z9="",U9,Z9+MAX(MIN(U9-Z9,Rules!$B$23),-Rules!$B$23))</f>
+        <v>2.94017094017094</v>
+      </c>
+      <c r="AB9" s="7" t="n">
+        <f aca="false">X9*(1+AA9)</f>
+        <v>2.19246871794872</v>
+      </c>
+      <c r="AC9" s="32" t="n">
+        <f aca="false">F9/Rules!$B$26*7</f>
+        <v>15.0862068965517</v>
+      </c>
+      <c r="AD9" s="7" t="n">
+        <f aca="false">IF(LEFT(Q9,2)="No",0,AC9*O9*(1+Y9))</f>
+        <v>8.39456896551724</v>
+      </c>
+      <c r="AE9" s="21" t="n">
+        <f aca="false">IF(LEFT(Q9,2)="No",0,AC9*N9)</f>
+        <v>0.313881520778073</v>
+      </c>
+      <c r="AF9" s="10" t="n">
+        <f aca="false">IF(OR(AE9=0,L9=0),"",AD9/(AE9*L9))</f>
+        <v>0.990899863799321</v>
+      </c>
+      <c r="AG9" s="8" t="str">
+        <f aca="false">IF(OR(LEFT(Q9,2)="No",D9="PAUSED",ABS(Y9)&gt;Rules!$B$25,AA9&lt;&gt;Z9),"Joseph","Shayan")</f>
+        <v>Joseph</v>
+      </c>
+      <c r="AH9" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI9" s="22"/>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$E$6:$E$45,MATCH($A10,Campaigns!$A$6:$A$45,0))</f>
+        <v>Boho core</v>
+      </c>
+      <c r="D10" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($A10,Campaigns!$A$6:$A$45,0))</f>
+        <v>PAUSED</v>
+      </c>
+      <c r="E10" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$G$6:$G$45,MATCH($A10,Campaigns!$A$6:$A$45,0))</f>
+        <v>Phase 0: stop list</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$AH$6:$AH$45,MATCH($A10,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AJ$6:$AJ$45,MATCH($A10,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AL$6:$AL$45,MATCH($A10,Campaigns!$A$6:$A$45,0))</f>
+        <v>50</v>
+      </c>
+      <c r="G10" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$AI$6:$AI$45,MATCH($A10,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AK$6:$AK$45,MATCH($A10,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AM$6:$AM$45,MATCH($A10,Campaigns!$A$6:$A$45,0))</f>
+        <v>44.85</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($A10,Campaigns!$A$6:$A$45,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$Q$6:$Q$45,MATCH($A10,Campaigns!$A$6:$A$45,0))</f>
+        <v>61.98</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$Y$6:$Y$45,MATCH($A10,Campaigns!$A$6:$A$45,0))</f>
+        <v>2</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <f aca="false">IF(I10=0,AVERAGE(Rules!$B$15,Rules!$B$16),J10/I10)</f>
+        <v>30.99</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <f aca="false">IF(F10=0,0,G10/F10)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N10" s="10" t="n">
+        <f aca="false">(G10+Rules!$B$37*Rules!$B$20)/(F10+Rules!$B$20)</f>
+        <v>0.0264102564102564</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <f aca="false">IF(F10=0,0,H10/F10)</f>
+        <v>0.897</v>
+      </c>
+      <c r="P10" s="10" t="n">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($A10,Campaigns!$A$6:$A$45,0))</f>
+        <v>0.723620522749274</v>
+      </c>
+      <c r="Q10" s="19" t="str">
+        <f aca="false">IF(C10="Brand defence","Brand defence: keep on",IF(G10=0,"No on-Amazon orders: pause",IF(K10&gt;0,IF(D10="ENABLED","Converting now: keep, optimize","Converting now: re-enable, optimize"),IF(D10="ENABLED","Converted before: keep, optimize","Converted before: re-enable, optimize"))))</f>
+        <v>Converting now: re-enable, optimize</v>
+      </c>
+      <c r="R10" s="7" t="n">
+        <f aca="false">Rules!$B$19*L10*N10</f>
+        <v>0.311012461538462</v>
+      </c>
+      <c r="S10" s="7" t="n">
+        <f aca="false">MAX(Rules!$B$24,R10*Rules!$B$39)</f>
+        <v>0.157867496746204</v>
+      </c>
+      <c r="T10" s="7" t="n">
+        <f aca="false">R10*Rules!$B$38</f>
+        <v>0.622024923076923</v>
+      </c>
+      <c r="U10" s="20" t="n">
+        <f aca="false">MAX(0,MIN(Rules!$B$9,T10/S10-1))</f>
+        <v>2.94017094017094</v>
+      </c>
+      <c r="V10" s="7" t="n">
+        <f aca="false">IF(O10=0,Rules!$B$7,O10)</f>
+        <v>0.897</v>
+      </c>
+      <c r="W10" s="10" t="n">
+        <f aca="false">IF(V10=0,0,S10/V10-1)</f>
+        <v>-0.824005020349829</v>
+      </c>
+      <c r="X10" s="7" t="n">
+        <f aca="false">IF(W10&lt;0,MAX(S10,V10*(1-Rules!$B$21)),MIN(S10,V10*(1+Rules!$B$22)))</f>
+        <v>0.67275</v>
+      </c>
+      <c r="Y10" s="10" t="n">
+        <f aca="false">IF(V10=0,0,X10/V10-1)</f>
+        <v>-0.25</v>
+      </c>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20" t="n">
+        <f aca="false">IF(Z10="",U10,Z10+MAX(MIN(U10-Z10,Rules!$B$23),-Rules!$B$23))</f>
+        <v>2.94017094017094</v>
+      </c>
+      <c r="AB10" s="7" t="n">
+        <f aca="false">X10*(1+AA10)</f>
+        <v>2.65075</v>
+      </c>
+      <c r="AC10" s="32" t="n">
+        <f aca="false">F10/Rules!$B$26*7</f>
+        <v>6.03448275862069</v>
+      </c>
+      <c r="AD10" s="7" t="n">
+        <f aca="false">IF(LEFT(Q10,2)="No",0,AC10*O10*(1+Y10))</f>
+        <v>4.05969827586207</v>
+      </c>
+      <c r="AE10" s="21" t="n">
+        <f aca="false">IF(LEFT(Q10,2)="No",0,AC10*N10)</f>
+        <v>0.159372236958444</v>
+      </c>
+      <c r="AF10" s="10" t="n">
+        <f aca="false">IF(OR(AE10=0,L10=0),"",AD10/(AE10*L10))</f>
+        <v>0.821976710307428</v>
+      </c>
+      <c r="AG10" s="8" t="str">
+        <f aca="false">IF(OR(LEFT(Q10,2)="No",D10="PAUSED",ABS(Y10)&gt;Rules!$B$25,AA10&lt;&gt;Z10),"Joseph","Shayan")</f>
+        <v>Joseph</v>
+      </c>
+      <c r="AH10" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI10" s="22"/>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$E$6:$E$45,MATCH($A11,Campaigns!$A$6:$A$45,0))</f>
+        <v>Boho couch / bed</v>
+      </c>
+      <c r="D11" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($A11,Campaigns!$A$6:$A$45,0))</f>
+        <v>ENABLED</v>
+      </c>
+      <c r="E11" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$G$6:$G$45,MATCH($A11,Campaigns!$A$6:$A$45,0))</f>
+        <v>Not in Phase 0</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$AH$6:$AH$45,MATCH($A11,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AJ$6:$AJ$45,MATCH($A11,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AL$6:$AL$45,MATCH($A11,Campaigns!$A$6:$A$45,0))</f>
+        <v>54</v>
+      </c>
+      <c r="G11" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$AI$6:$AI$45,MATCH($A11,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AK$6:$AK$45,MATCH($A11,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AM$6:$AM$45,MATCH($A11,Campaigns!$A$6:$A$45,0))</f>
+        <v>79.73</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($A11,Campaigns!$A$6:$A$45,0))</f>
+        <v>5</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$Q$6:$Q$45,MATCH($A11,Campaigns!$A$6:$A$45,0))</f>
+        <v>150.95</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$Y$6:$Y$45,MATCH($A11,Campaigns!$A$6:$A$45,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <f aca="false">IF(I11=0,AVERAGE(Rules!$B$15,Rules!$B$16),J11/I11)</f>
+        <v>30.19</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <f aca="false">IF(F11=0,0,G11/F11)</f>
+        <v>0.0185185185185185</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <f aca="false">(G11+Rules!$B$37*Rules!$B$20)/(F11+Rules!$B$20)</f>
+        <v>0.0157790927021696</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <f aca="false">IF(F11=0,0,H11/F11)</f>
+        <v>1.47648148148148</v>
+      </c>
+      <c r="P11" s="10" t="n">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($A11,Campaigns!$A$6:$A$45,0))</f>
+        <v>1.05319642265651</v>
+      </c>
+      <c r="Q11" s="19" t="str">
+        <f aca="false">IF(C11="Brand defence","Brand defence: keep on",IF(G11=0,"No on-Amazon orders: pause",IF(K11&gt;0,IF(D11="ENABLED","Converting now: keep, optimize","Converting now: re-enable, optimize"),IF(D11="ENABLED","Converted before: keep, optimize","Converted before: re-enable, optimize"))))</f>
+        <v>Converted before: keep, optimize</v>
+      </c>
+      <c r="R11" s="7" t="n">
+        <f aca="false">Rules!$B$19*L11*N11</f>
+        <v>0.18102090729783</v>
+      </c>
+      <c r="S11" s="7" t="n">
+        <f aca="false">MAX(Rules!$B$24,R11*Rules!$B$39)</f>
+        <v>0.1</v>
+      </c>
+      <c r="T11" s="7" t="n">
+        <f aca="false">R11*Rules!$B$38</f>
+        <v>0.362041814595661</v>
+      </c>
+      <c r="U11" s="20" t="n">
+        <f aca="false">MAX(0,MIN(Rules!$B$9,T11/S11-1))</f>
+        <v>2.62041814595661</v>
+      </c>
+      <c r="V11" s="7" t="n">
+        <f aca="false">IF(O11=0,Rules!$B$7,O11)</f>
+        <v>1.47648148148148</v>
+      </c>
+      <c r="W11" s="10" t="n">
+        <f aca="false">IF(V11=0,0,S11/V11-1)</f>
+        <v>-0.932271416029098</v>
+      </c>
+      <c r="X11" s="7" t="n">
+        <f aca="false">IF(W11&lt;0,MAX(S11,V11*(1-Rules!$B$21)),MIN(S11,V11*(1+Rules!$B$22)))</f>
+        <v>1.10736111111111</v>
+      </c>
+      <c r="Y11" s="10" t="n">
+        <f aca="false">IF(V11=0,0,X11/V11-1)</f>
+        <v>-0.25</v>
+      </c>
+      <c r="Z11" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA11" s="20" t="n">
+        <f aca="false">IF(Z11="",U11,Z11+MAX(MIN(U11-Z11,Rules!$B$23),-Rules!$B$23))</f>
+        <v>2.8</v>
+      </c>
+      <c r="AB11" s="7" t="n">
+        <f aca="false">X11*(1+AA11)</f>
+        <v>4.20797222222222</v>
+      </c>
+      <c r="AC11" s="32" t="n">
+        <f aca="false">F11/Rules!$B$26*7</f>
+        <v>6.51724137931034</v>
+      </c>
+      <c r="AD11" s="7" t="n">
+        <f aca="false">IF(LEFT(Q11,2)="No",0,AC11*O11*(1+Y11))</f>
+        <v>7.21693965517241</v>
+      </c>
+      <c r="AE11" s="21" t="n">
+        <f aca="false">IF(LEFT(Q11,2)="No",0,AC11*N11)</f>
+        <v>0.102836155886554</v>
+      </c>
+      <c r="AF11" s="10" t="n">
+        <f aca="false">IF(OR(AE11=0,L11=0),"",AD11/(AE11*L11))</f>
+        <v>2.32457801976372</v>
+      </c>
+      <c r="AG11" s="8" t="str">
+        <f aca="false">IF(OR(LEFT(Q11,2)="No",D11="PAUSED",ABS(Y11)&gt;Rules!$B$25,AA11&lt;&gt;Z11),"Joseph","Shayan")</f>
+        <v>Joseph</v>
+      </c>
+      <c r="AH11" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI11" s="22"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$E$6:$E$45,MATCH($A12,Campaigns!$A$6:$A$45,0))</f>
+        <v>Competitor PAT</v>
+      </c>
+      <c r="D12" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($A12,Campaigns!$A$6:$A$45,0))</f>
+        <v>ENABLED</v>
+      </c>
+      <c r="E12" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$G$6:$G$45,MATCH($A12,Campaigns!$A$6:$A$45,0))</f>
+        <v>Not in Phase 0 (Phase 1 lane L9)</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$AH$6:$AH$45,MATCH($A12,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AJ$6:$AJ$45,MATCH($A12,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AL$6:$AL$45,MATCH($A12,Campaigns!$A$6:$A$45,0))</f>
+        <v>67</v>
+      </c>
+      <c r="G12" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$AI$6:$AI$45,MATCH($A12,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AK$6:$AK$45,MATCH($A12,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AM$6:$AM$45,MATCH($A12,Campaigns!$A$6:$A$45,0))</f>
+        <v>103.08</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($A12,Campaigns!$A$6:$A$45,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$Q$6:$Q$45,MATCH($A12,Campaigns!$A$6:$A$45,0))</f>
+        <v>34.99</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$Y$6:$Y$45,MATCH($A12,Campaigns!$A$6:$A$45,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <f aca="false">IF(I12=0,AVERAGE(Rules!$B$15,Rules!$B$16),J12/I12)</f>
+        <v>34.99</v>
+      </c>
+      <c r="M12" s="10" t="n">
+        <f aca="false">IF(F12=0,0,G12/F12)</f>
+        <v>0.0149253731343284</v>
+      </c>
+      <c r="N12" s="10" t="n">
+        <f aca="false">(G12+Rules!$B$37*Rules!$B$20)/(F12+Rules!$B$20)</f>
+        <v>0.0140258601797063</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <f aca="false">IF(F12=0,0,H12/F12)</f>
+        <v>1.53850746268657</v>
+      </c>
+      <c r="P12" s="10" t="n">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($A12,Campaigns!$A$6:$A$45,0))</f>
+        <v>2.94598456701915</v>
+      </c>
+      <c r="Q12" s="19" t="str">
+        <f aca="false">IF(C12="Brand defence","Brand defence: keep on",IF(G12=0,"No on-Amazon orders: pause",IF(K12&gt;0,IF(D12="ENABLED","Converting now: keep, optimize","Converting now: re-enable, optimize"),IF(D12="ENABLED","Converted before: keep, optimize","Converted before: re-enable, optimize"))))</f>
+        <v>Converting now: keep, optimize</v>
+      </c>
+      <c r="R12" s="7" t="n">
+        <f aca="false">Rules!$B$19*L12*N12</f>
+        <v>0.186490642121411</v>
+      </c>
+      <c r="S12" s="7" t="n">
+        <f aca="false">MAX(Rules!$B$24,R12*Rules!$B$39)</f>
+        <v>0.1</v>
+      </c>
+      <c r="T12" s="7" t="n">
+        <f aca="false">R12*Rules!$B$38</f>
+        <v>0.372981284242823</v>
+      </c>
+      <c r="U12" s="20" t="n">
+        <f aca="false">MAX(0,MIN(Rules!$B$9,T12/S12-1))</f>
+        <v>2.72981284242823</v>
+      </c>
+      <c r="V12" s="7" t="n">
+        <f aca="false">IF(O12=0,Rules!$B$7,O12)</f>
+        <v>1.53850746268657</v>
+      </c>
+      <c r="W12" s="10" t="n">
+        <f aca="false">IF(V12=0,0,S12/V12-1)</f>
+        <v>-0.93500194024059</v>
+      </c>
+      <c r="X12" s="7" t="n">
+        <f aca="false">IF(W12&lt;0,MAX(S12,V12*(1-Rules!$B$21)),MIN(S12,V12*(1+Rules!$B$22)))</f>
+        <v>1.15388059701493</v>
+      </c>
+      <c r="Y12" s="10" t="n">
+        <f aca="false">IF(V12=0,0,X12/V12-1)</f>
+        <v>-0.25</v>
+      </c>
+      <c r="Z12" s="31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA12" s="20" t="n">
+        <f aca="false">IF(Z12="",U12,Z12+MAX(MIN(U12-Z12,Rules!$B$23),-Rules!$B$23))</f>
+        <v>2.72981284242823</v>
+      </c>
+      <c r="AB12" s="7" t="n">
+        <f aca="false">X12*(1+AA12)</f>
+        <v>4.30375866937502</v>
+      </c>
+      <c r="AC12" s="32" t="n">
+        <f aca="false">F12/Rules!$B$26*7</f>
+        <v>8.08620689655172</v>
+      </c>
+      <c r="AD12" s="7" t="n">
+        <f aca="false">IF(LEFT(Q12,2)="No",0,AC12*O12*(1+Y12))</f>
+        <v>9.33051724137931</v>
+      </c>
+      <c r="AE12" s="21" t="n">
+        <f aca="false">IF(LEFT(Q12,2)="No",0,AC12*N12)</f>
+        <v>0.113416007315212</v>
+      </c>
+      <c r="AF12" s="10" t="n">
+        <f aca="false">IF(OR(AE12=0,L12=0),"",AD12/(AE12*L12))</f>
+        <v>2.35118835925403</v>
+      </c>
+      <c r="AG12" s="8" t="str">
+        <f aca="false">IF(OR(LEFT(Q12,2)="No",D12="PAUSED",ABS(Y12)&gt;Rules!$B$25,AA12&lt;&gt;Z12),"Joseph","Shayan")</f>
+        <v>Joseph</v>
+      </c>
+      <c r="AH12" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI12" s="22"/>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="C13" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$E$6:$E$45,MATCH($A13,Campaigns!$A$6:$A$45,0))</f>
+        <v>Boho material (cotton)</v>
+      </c>
+      <c r="D13" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($A13,Campaigns!$A$6:$A$45,0))</f>
+        <v>PAUSED</v>
+      </c>
+      <c r="E13" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$G$6:$G$45,MATCH($A13,Campaigns!$A$6:$A$45,0))</f>
+        <v>Not in Phase 0</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$AH$6:$AH$45,MATCH($A13,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AJ$6:$AJ$45,MATCH($A13,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AL$6:$AL$45,MATCH($A13,Campaigns!$A$6:$A$45,0))</f>
+        <v>62</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$AI$6:$AI$45,MATCH($A13,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AK$6:$AK$45,MATCH($A13,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AM$6:$AM$45,MATCH($A13,Campaigns!$A$6:$A$45,0))</f>
+        <v>60</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($A13,Campaigns!$A$6:$A$45,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$Q$6:$Q$45,MATCH($A13,Campaigns!$A$6:$A$45,0))</f>
+        <v>26.99</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$Y$6:$Y$45,MATCH($A13,Campaigns!$A$6:$A$45,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <f aca="false">IF(I13=0,AVERAGE(Rules!$B$15,Rules!$B$16),J13/I13)</f>
+        <v>26.99</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <f aca="false">IF(F13=0,0,G13/F13)</f>
+        <v>0.0161290322580645</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <f aca="false">(G13+Rules!$B$37*Rules!$B$20)/(F13+Rules!$B$20)</f>
+        <v>0.0146520146520147</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <f aca="false">IF(F13=0,0,H13/F13)</f>
+        <v>0.967741935483871</v>
+      </c>
+      <c r="P13" s="10" t="n">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($A13,Campaigns!$A$6:$A$45,0))</f>
+        <v>2.33308632826973</v>
+      </c>
+      <c r="Q13" s="19" t="str">
+        <f aca="false">IF(C13="Brand defence","Brand defence: keep on",IF(G13=0,"No on-Amazon orders: pause",IF(K13&gt;0,IF(D13="ENABLED","Converting now: keep, optimize","Converting now: re-enable, optimize"),IF(D13="ENABLED","Converted before: keep, optimize","Converted before: re-enable, optimize"))))</f>
+        <v>Converted before: re-enable, optimize</v>
+      </c>
+      <c r="R13" s="7" t="n">
+        <f aca="false">Rules!$B$19*L13*N13</f>
+        <v>0.150273992673993</v>
+      </c>
+      <c r="S13" s="7" t="n">
+        <f aca="false">MAX(Rules!$B$24,R13*Rules!$B$39)</f>
+        <v>0.1</v>
+      </c>
+      <c r="T13" s="7" t="n">
+        <f aca="false">R13*Rules!$B$38</f>
+        <v>0.300547985347985</v>
+      </c>
+      <c r="U13" s="20" t="n">
+        <f aca="false">MAX(0,MIN(Rules!$B$9,T13/S13-1))</f>
+        <v>2.00547985347985</v>
+      </c>
+      <c r="V13" s="7" t="n">
+        <f aca="false">IF(O13=0,Rules!$B$7,O13)</f>
+        <v>0.967741935483871</v>
+      </c>
+      <c r="W13" s="10" t="n">
+        <f aca="false">IF(V13=0,0,S13/V13-1)</f>
+        <v>-0.896666666666667</v>
+      </c>
+      <c r="X13" s="7" t="n">
+        <f aca="false">IF(W13&lt;0,MAX(S13,V13*(1-Rules!$B$21)),MIN(S13,V13*(1+Rules!$B$22)))</f>
+        <v>0.725806451612903</v>
+      </c>
+      <c r="Y13" s="10" t="n">
+        <f aca="false">IF(V13=0,0,X13/V13-1)</f>
+        <v>-0.25</v>
+      </c>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="20" t="n">
+        <f aca="false">IF(Z13="",U13,Z13+MAX(MIN(U13-Z13,Rules!$B$23),-Rules!$B$23))</f>
+        <v>2.00547985347985</v>
+      </c>
+      <c r="AB13" s="7" t="n">
+        <f aca="false">X13*(1+AA13)</f>
+        <v>2.18139666784828</v>
+      </c>
+      <c r="AC13" s="32" t="n">
+        <f aca="false">F13/Rules!$B$26*7</f>
+        <v>7.48275862068966</v>
+      </c>
+      <c r="AD13" s="7" t="n">
+        <f aca="false">IF(LEFT(Q13,2)="No",0,AC13*O13*(1+Y13))</f>
+        <v>5.43103448275862</v>
+      </c>
+      <c r="AE13" s="21" t="n">
+        <f aca="false">IF(LEFT(Q13,2)="No",0,AC13*N13)</f>
+        <v>0.109637488947834</v>
+      </c>
+      <c r="AF13" s="10" t="n">
+        <f aca="false">IF(OR(AE13=0,L13=0),"",AD13/(AE13*L13))</f>
+        <v>1.83535718127383</v>
+      </c>
+      <c r="AG13" s="8" t="str">
+        <f aca="false">IF(OR(LEFT(Q13,2)="No",D13="PAUSED",ABS(Y13)&gt;Rules!$B$25,AA13&lt;&gt;Z13),"Joseph","Shayan")</f>
+        <v>Joseph</v>
+      </c>
+      <c r="AH13" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI13" s="22"/>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C14" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$E$6:$E$45,MATCH($A14,Campaigns!$A$6:$A$45,0))</f>
+        <v>Boho material (cotton)</v>
+      </c>
+      <c r="D14" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($A14,Campaigns!$A$6:$A$45,0))</f>
+        <v>PAUSED</v>
+      </c>
+      <c r="E14" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$G$6:$G$45,MATCH($A14,Campaigns!$A$6:$A$45,0))</f>
+        <v>Not in Phase 0</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$AH$6:$AH$45,MATCH($A14,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AJ$6:$AJ$45,MATCH($A14,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AL$6:$AL$45,MATCH($A14,Campaigns!$A$6:$A$45,0))</f>
+        <v>35</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$AI$6:$AI$45,MATCH($A14,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AK$6:$AK$45,MATCH($A14,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AM$6:$AM$45,MATCH($A14,Campaigns!$A$6:$A$45,0))</f>
+        <v>36.98</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($A14,Campaigns!$A$6:$A$45,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$Q$6:$Q$45,MATCH($A14,Campaigns!$A$6:$A$45,0))</f>
+        <v>34.99</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$Y$6:$Y$45,MATCH($A14,Campaigns!$A$6:$A$45,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <f aca="false">IF(I14=0,AVERAGE(Rules!$B$15,Rules!$B$16),J14/I14)</f>
+        <v>34.99</v>
+      </c>
+      <c r="M14" s="10" t="n">
+        <f aca="false">IF(F14=0,0,G14/F14)</f>
+        <v>0.0285714285714286</v>
+      </c>
+      <c r="N14" s="10" t="n">
+        <f aca="false">(G14+Rules!$B$37*Rules!$B$20)/(F14+Rules!$B$20)</f>
+        <v>0.0193061840120664</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <f aca="false">IF(F14=0,0,H14/F14)</f>
+        <v>1.05657142857143</v>
+      </c>
+      <c r="P14" s="10" t="n">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($A14,Campaigns!$A$6:$A$45,0))</f>
+        <v>1.05687339239783</v>
+      </c>
+      <c r="Q14" s="19" t="str">
+        <f aca="false">IF(C14="Brand defence","Brand defence: keep on",IF(G14=0,"No on-Amazon orders: pause",IF(K14&gt;0,IF(D14="ENABLED","Converting now: keep, optimize","Converting now: re-enable, optimize"),IF(D14="ENABLED","Converted before: keep, optimize","Converted before: re-enable, optimize"))))</f>
+        <v>Converted before: re-enable, optimize</v>
+      </c>
+      <c r="R14" s="7" t="n">
+        <f aca="false">Rules!$B$19*L14*N14</f>
+        <v>0.256698883861237</v>
+      </c>
+      <c r="S14" s="7" t="n">
+        <f aca="false">MAX(Rules!$B$24,R14*Rules!$B$39)</f>
+        <v>0.130298348857981</v>
+      </c>
+      <c r="T14" s="7" t="n">
+        <f aca="false">R14*Rules!$B$38</f>
+        <v>0.513397767722474</v>
+      </c>
+      <c r="U14" s="20" t="n">
+        <f aca="false">MAX(0,MIN(Rules!$B$9,T14/S14-1))</f>
+        <v>2.94017094017094</v>
+      </c>
+      <c r="V14" s="7" t="n">
+        <f aca="false">IF(O14=0,Rules!$B$7,O14)</f>
+        <v>1.05657142857143</v>
+      </c>
+      <c r="W14" s="10" t="n">
+        <f aca="false">IF(V14=0,0,S14/V14-1)</f>
+        <v>-0.876678144672002</v>
+      </c>
+      <c r="X14" s="7" t="n">
+        <f aca="false">IF(W14&lt;0,MAX(S14,V14*(1-Rules!$B$21)),MIN(S14,V14*(1+Rules!$B$22)))</f>
+        <v>0.792428571428571</v>
+      </c>
+      <c r="Y14" s="10" t="n">
+        <f aca="false">IF(V14=0,0,X14/V14-1)</f>
+        <v>-0.25</v>
+      </c>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="20" t="n">
+        <f aca="false">IF(Z14="",U14,Z14+MAX(MIN(U14-Z14,Rules!$B$23),-Rules!$B$23))</f>
+        <v>2.94017094017094</v>
+      </c>
+      <c r="AB14" s="7" t="n">
+        <f aca="false">X14*(1+AA14)</f>
+        <v>3.12230402930403</v>
+      </c>
+      <c r="AC14" s="32" t="n">
+        <f aca="false">F14/Rules!$B$26*7</f>
+        <v>4.22413793103448</v>
+      </c>
+      <c r="AD14" s="7" t="n">
+        <f aca="false">IF(LEFT(Q14,2)="No",0,AC14*O14*(1+Y14))</f>
+        <v>3.3473275862069</v>
+      </c>
+      <c r="AE14" s="21" t="n">
+        <f aca="false">IF(LEFT(Q14,2)="No",0,AC14*N14)</f>
+        <v>0.081551984188901</v>
+      </c>
+      <c r="AF14" s="10" t="n">
+        <f aca="false">IF(OR(AE14=0,L14=0),"",AD14/(AE14*L14))</f>
+        <v>1.17305869278978</v>
+      </c>
+      <c r="AG14" s="8" t="str">
+        <f aca="false">IF(OR(LEFT(Q14,2)="No",D14="PAUSED",ABS(Y14)&gt;Rules!$B$25,AA14&lt;&gt;Z14),"Joseph","Shayan")</f>
+        <v>Joseph</v>
+      </c>
+      <c r="AH14" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI14" s="22"/>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C15" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$E$6:$E$45,MATCH($A15,Campaigns!$A$6:$A$45,0))</f>
+        <v>Boho couch / bed</v>
+      </c>
+      <c r="D15" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($A15,Campaigns!$A$6:$A$45,0))</f>
+        <v>PAUSED</v>
+      </c>
+      <c r="E15" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$G$6:$G$45,MATCH($A15,Campaigns!$A$6:$A$45,0))</f>
+        <v>Not in Phase 0</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$AH$6:$AH$45,MATCH($A15,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AJ$6:$AJ$45,MATCH($A15,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AL$6:$AL$45,MATCH($A15,Campaigns!$A$6:$A$45,0))</f>
+        <v>26</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$AI$6:$AI$45,MATCH($A15,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AK$6:$AK$45,MATCH($A15,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AM$6:$AM$45,MATCH($A15,Campaigns!$A$6:$A$45,0))</f>
+        <v>30.49</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($A15,Campaigns!$A$6:$A$45,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$Q$6:$Q$45,MATCH($A15,Campaigns!$A$6:$A$45,0))</f>
+        <v>34.99</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$Y$6:$Y$45,MATCH($A15,Campaigns!$A$6:$A$45,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <f aca="false">IF(I15=0,AVERAGE(Rules!$B$15,Rules!$B$16),J15/I15)</f>
+        <v>34.99</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <f aca="false">IF(F15=0,0,G15/F15)</f>
+        <v>0.0384615384615385</v>
+      </c>
+      <c r="N15" s="10" t="n">
+        <f aca="false">(G15+Rules!$B$37*Rules!$B$20)/(F15+Rules!$B$20)</f>
+        <v>0.0215924426450742</v>
+      </c>
+      <c r="O15" s="7" t="n">
+        <f aca="false">IF(F15=0,0,H15/F15)</f>
+        <v>1.17269230769231</v>
+      </c>
+      <c r="P15" s="10" t="n">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($A15,Campaigns!$A$6:$A$45,0))</f>
+        <v>0.940268648185196</v>
+      </c>
+      <c r="Q15" s="19" t="str">
+        <f aca="false">IF(C15="Brand defence","Brand defence: keep on",IF(G15=0,"No on-Amazon orders: pause",IF(K15&gt;0,IF(D15="ENABLED","Converting now: keep, optimize","Converting now: re-enable, optimize"),IF(D15="ENABLED","Converted before: keep, optimize","Converted before: re-enable, optimize"))))</f>
+        <v>Converted before: re-enable, optimize</v>
+      </c>
+      <c r="R15" s="7" t="n">
+        <f aca="false">Rules!$B$19*L15*N15</f>
+        <v>0.287097435897436</v>
+      </c>
+      <c r="S15" s="7" t="n">
+        <f aca="false">MAX(Rules!$B$24,R15*Rules!$B$39)</f>
+        <v>0.1457284164859</v>
+      </c>
+      <c r="T15" s="7" t="n">
+        <f aca="false">R15*Rules!$B$38</f>
+        <v>0.574194871794872</v>
+      </c>
+      <c r="U15" s="20" t="n">
+        <f aca="false">MAX(0,MIN(Rules!$B$9,T15/S15-1))</f>
+        <v>2.94017094017094</v>
+      </c>
+      <c r="V15" s="7" t="n">
+        <f aca="false">IF(O15=0,Rules!$B$7,O15)</f>
+        <v>1.17269230769231</v>
+      </c>
+      <c r="W15" s="10" t="n">
+        <f aca="false">IF(V15=0,0,S15/V15-1)</f>
+        <v>-0.875731753734556</v>
+      </c>
+      <c r="X15" s="7" t="n">
+        <f aca="false">IF(W15&lt;0,MAX(S15,V15*(1-Rules!$B$21)),MIN(S15,V15*(1+Rules!$B$22)))</f>
+        <v>0.879519230769231</v>
+      </c>
+      <c r="Y15" s="10" t="n">
+        <f aca="false">IF(V15=0,0,X15/V15-1)</f>
+        <v>-0.25</v>
+      </c>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="20" t="n">
+        <f aca="false">IF(Z15="",U15,Z15+MAX(MIN(U15-Z15,Rules!$B$23),-Rules!$B$23))</f>
+        <v>2.94017094017094</v>
+      </c>
+      <c r="AB15" s="7" t="n">
+        <f aca="false">X15*(1+AA15)</f>
+        <v>3.46545611439842</v>
+      </c>
+      <c r="AC15" s="32" t="n">
+        <f aca="false">F15/Rules!$B$26*7</f>
+        <v>3.13793103448276</v>
+      </c>
+      <c r="AD15" s="7" t="n">
+        <f aca="false">IF(LEFT(Q15,2)="No",0,AC15*O15*(1+Y15))</f>
+        <v>2.75987068965517</v>
+      </c>
+      <c r="AE15" s="21" t="n">
+        <f aca="false">IF(LEFT(Q15,2)="No",0,AC15*N15)</f>
+        <v>0.0677555958862674</v>
+      </c>
+      <c r="AF15" s="10" t="n">
+        <f aca="false">IF(OR(AE15=0,L15=0),"",AD15/(AE15*L15))</f>
+        <v>1.16412501786225</v>
+      </c>
+      <c r="AG15" s="8" t="str">
+        <f aca="false">IF(OR(LEFT(Q15,2)="No",D15="PAUSED",ABS(Y15)&gt;Rules!$B$25,AA15&lt;&gt;Z15),"Joseph","Shayan")</f>
+        <v>Joseph</v>
+      </c>
+      <c r="AH15" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI15" s="22"/>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C16" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$E$6:$E$45,MATCH($A16,Campaigns!$A$6:$A$45,0))</f>
+        <v>Boho pattern / colour</v>
+      </c>
+      <c r="D16" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($A16,Campaigns!$A$6:$A$45,0))</f>
+        <v>ENABLED</v>
+      </c>
+      <c r="E16" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$G$6:$G$45,MATCH($A16,Campaigns!$A$6:$A$45,0))</f>
+        <v>Not in Phase 0</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$AH$6:$AH$45,MATCH($A16,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AJ$6:$AJ$45,MATCH($A16,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AL$6:$AL$45,MATCH($A16,Campaigns!$A$6:$A$45,0))</f>
+        <v>7</v>
+      </c>
+      <c r="G16" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$AI$6:$AI$45,MATCH($A16,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AK$6:$AK$45,MATCH($A16,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AM$6:$AM$45,MATCH($A16,Campaigns!$A$6:$A$45,0))</f>
+        <v>10.7</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($A16,Campaigns!$A$6:$A$45,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$Q$6:$Q$45,MATCH($A16,Campaigns!$A$6:$A$45,0))</f>
+        <v>34.99</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$Y$6:$Y$45,MATCH($A16,Campaigns!$A$6:$A$45,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <f aca="false">IF(I16=0,AVERAGE(Rules!$B$15,Rules!$B$16),J16/I16)</f>
+        <v>34.99</v>
+      </c>
+      <c r="M16" s="10" t="n">
+        <f aca="false">IF(F16=0,0,G16/F16)</f>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="N16" s="10" t="n">
+        <f aca="false">(G16+Rules!$B$37*Rules!$B$20)/(F16+Rules!$B$20)</f>
+        <v>0.0287899235267656</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <f aca="false">IF(F16=0,0,H16/F16)</f>
+        <v>1.52857142857143</v>
+      </c>
+      <c r="P16" s="10" t="n">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($A16,Campaigns!$A$6:$A$45,0))</f>
+        <v>0.305801657616462</v>
+      </c>
+      <c r="Q16" s="19" t="str">
+        <f aca="false">IF(C16="Brand defence","Brand defence: keep on",IF(G16=0,"No on-Amazon orders: pause",IF(K16&gt;0,IF(D16="ENABLED","Converting now: keep, optimize","Converting now: re-enable, optimize"),IF(D16="ENABLED","Converted before: keep, optimize","Converted before: re-enable, optimize"))))</f>
+        <v>Converted before: keep, optimize</v>
+      </c>
+      <c r="R16" s="7" t="n">
+        <f aca="false">Rules!$B$19*L16*N16</f>
+        <v>0.382796581196581</v>
+      </c>
+      <c r="S16" s="7" t="n">
+        <f aca="false">MAX(Rules!$B$24,R16*Rules!$B$39)</f>
+        <v>0.194304555314534</v>
+      </c>
+      <c r="T16" s="7" t="n">
+        <f aca="false">R16*Rules!$B$38</f>
+        <v>0.765593162393162</v>
+      </c>
+      <c r="U16" s="20" t="n">
+        <f aca="false">MAX(0,MIN(Rules!$B$9,T16/S16-1))</f>
+        <v>2.94017094017094</v>
+      </c>
+      <c r="V16" s="7" t="n">
+        <f aca="false">IF(O16=0,Rules!$B$7,O16)</f>
+        <v>1.52857142857143</v>
+      </c>
+      <c r="W16" s="10" t="n">
+        <f aca="false">IF(V16=0,0,S16/V16-1)</f>
+        <v>-0.872884870354978</v>
+      </c>
+      <c r="X16" s="7" t="n">
+        <f aca="false">IF(W16&lt;0,MAX(S16,V16*(1-Rules!$B$21)),MIN(S16,V16*(1+Rules!$B$22)))</f>
+        <v>1.14642857142857</v>
+      </c>
+      <c r="Y16" s="10" t="n">
+        <f aca="false">IF(V16=0,0,X16/V16-1)</f>
+        <v>-0.25</v>
+      </c>
+      <c r="Z16" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA16" s="20" t="n">
+        <f aca="false">IF(Z16="",U16,Z16+MAX(MIN(U16-Z16,Rules!$B$23),-Rules!$B$23))</f>
+        <v>2.94017094017094</v>
+      </c>
+      <c r="AB16" s="7" t="n">
+        <f aca="false">X16*(1+AA16)</f>
+        <v>4.51712454212454</v>
+      </c>
+      <c r="AC16" s="32" t="n">
+        <f aca="false">F16/Rules!$B$26*7</f>
+        <v>0.844827586206897</v>
+      </c>
+      <c r="AD16" s="7" t="n">
+        <f aca="false">IF(LEFT(Q16,2)="No",0,AC16*O16*(1+Y16))</f>
+        <v>0.968534482758621</v>
+      </c>
+      <c r="AE16" s="21" t="n">
+        <f aca="false">IF(LEFT(Q16,2)="No",0,AC16*N16)</f>
+        <v>0.0243225216001986</v>
+      </c>
+      <c r="AF16" s="10" t="n">
+        <f aca="false">IF(OR(AE16=0,L16=0),"",AD16/(AE16*L16))</f>
+        <v>1.13805315549341</v>
+      </c>
+      <c r="AG16" s="8" t="str">
+        <f aca="false">IF(OR(LEFT(Q16,2)="No",D16="PAUSED",ABS(Y16)&gt;Rules!$B$25,AA16&lt;&gt;Z16),"Joseph","Shayan")</f>
+        <v>Joseph</v>
+      </c>
+      <c r="AH16" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI16" s="22"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="C17" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$E$6:$E$45,MATCH($A17,Campaigns!$A$6:$A$45,0))</f>
+        <v>Boho size (king / queen / 60x80)</v>
+      </c>
+      <c r="D17" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($A17,Campaigns!$A$6:$A$45,0))</f>
+        <v>ENABLED</v>
+      </c>
+      <c r="E17" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$G$6:$G$45,MATCH($A17,Campaigns!$A$6:$A$45,0))</f>
+        <v>Phase 0: run (as 'converting long tail')</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$AH$6:$AH$45,MATCH($A17,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AJ$6:$AJ$45,MATCH($A17,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AL$6:$AL$45,MATCH($A17,Campaigns!$A$6:$A$45,0))</f>
+        <v>36</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$AI$6:$AI$45,MATCH($A17,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AK$6:$AK$45,MATCH($A17,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AM$6:$AM$45,MATCH($A17,Campaigns!$A$6:$A$45,0))</f>
+        <v>44.1</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($A17,Campaigns!$A$6:$A$45,0))</f>
+        <v>9</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$Q$6:$Q$45,MATCH($A17,Campaigns!$A$6:$A$45,0))</f>
+        <v>282.91</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$Y$6:$Y$45,MATCH($A17,Campaigns!$A$6:$A$45,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <f aca="false">IF(I17=0,AVERAGE(Rules!$B$15,Rules!$B$16),J17/I17)</f>
+        <v>31.4344444444445</v>
+      </c>
+      <c r="M17" s="10" t="n">
+        <f aca="false">IF(F17=0,0,G17/F17)</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="10" t="n">
+        <f aca="false">(G17+Rules!$B$37*Rules!$B$20)/(F17+Rules!$B$20)</f>
+        <v>0.00745378652355396</v>
+      </c>
+      <c r="O17" s="7" t="n">
+        <f aca="false">IF(F17=0,0,H17/F17)</f>
+        <v>1.225</v>
+      </c>
+      <c r="P17" s="10" t="n">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($A17,Campaigns!$A$6:$A$45,0))</f>
+        <v>0.845604609239687</v>
+      </c>
+      <c r="Q17" s="19" t="str">
+        <f aca="false">IF(C17="Brand defence","Brand defence: keep on",IF(G17=0,"No on-Amazon orders: pause",IF(K17&gt;0,IF(D17="ENABLED","Converting now: keep, optimize","Converting now: re-enable, optimize"),IF(D17="ENABLED","Converted before: keep, optimize","Converted before: re-enable, optimize"))))</f>
+        <v>No on-Amazon orders: pause</v>
+      </c>
+      <c r="R17" s="7" t="n">
+        <f aca="false">Rules!$B$19*L17*N17</f>
+        <v>0.0890361425826542</v>
+      </c>
+      <c r="S17" s="7" t="n">
+        <f aca="false">MAX(Rules!$B$24,R17*Rules!$B$39)</f>
+        <v>0.1</v>
+      </c>
+      <c r="T17" s="7" t="n">
+        <f aca="false">R17*Rules!$B$38</f>
+        <v>0.178072285165308</v>
+      </c>
+      <c r="U17" s="20" t="n">
+        <f aca="false">MAX(0,MIN(Rules!$B$9,T17/S17-1))</f>
+        <v>0.780722851653084</v>
+      </c>
+      <c r="V17" s="33" t="n">
+        <f aca="false">0.97</f>
+        <v>0.97</v>
+      </c>
+      <c r="W17" s="10" t="n">
+        <f aca="false">IF(V17=0,0,S17/V17-1)</f>
+        <v>-0.896907216494845</v>
+      </c>
+      <c r="X17" s="7" t="n">
+        <f aca="false">IF(W17&lt;0,MAX(S17,V17*(1-Rules!$B$21)),MIN(S17,V17*(1+Rules!$B$22)))</f>
+        <v>0.7275</v>
+      </c>
+      <c r="Y17" s="10" t="n">
+        <f aca="false">IF(V17=0,0,X17/V17-1)</f>
+        <v>-0.25</v>
+      </c>
+      <c r="Z17" s="31" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AA17" s="20" t="n">
+        <f aca="false">IF(Z17="",U17,Z17+MAX(MIN(U17-Z17,Rules!$B$23),-Rules!$B$23))</f>
+        <v>3.93</v>
+      </c>
+      <c r="AB17" s="7" t="n">
+        <f aca="false">X17*(1+AA17)</f>
+        <v>3.586575</v>
+      </c>
+      <c r="AC17" s="32" t="n">
+        <f aca="false">F17/Rules!$B$26*7</f>
+        <v>4.3448275862069</v>
+      </c>
+      <c r="AD17" s="7" t="n">
+        <f aca="false">IF(LEFT(Q17,2)="No",0,AC17*O17*(1+Y17))</f>
+        <v>0</v>
+      </c>
+      <c r="AE17" s="21" t="n">
+        <f aca="false">IF(LEFT(Q17,2)="No",0,AC17*N17)</f>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="10" t="str">
+        <f aca="false">IF(OR(AE17=0,L17=0),"",AD17/(AE17*L17))</f>
+        <v/>
+      </c>
+      <c r="AG17" s="8" t="str">
+        <f aca="false">IF(OR(LEFT(Q17,2)="No",D17="PAUSED",ABS(Y17)&gt;Rules!$B$25,AA17&lt;&gt;Z17),"Joseph","Shayan")</f>
+        <v>Joseph</v>
+      </c>
+      <c r="AH17" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI17" s="22"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$E$6:$E$45,MATCH($A18,Campaigns!$A$6:$A$45,0))</f>
+        <v>Boho size (king / queen / 60x80)</v>
+      </c>
+      <c r="D18" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($A18,Campaigns!$A$6:$A$45,0))</f>
+        <v>ENABLED</v>
+      </c>
+      <c r="E18" s="8" t="str">
+        <f aca="false">INDEX(Campaigns!$G$6:$G$45,MATCH($A18,Campaigns!$A$6:$A$45,0))</f>
+        <v>Exclude list (king / queen)</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$AH$6:$AH$45,MATCH($A18,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AJ$6:$AJ$45,MATCH($A18,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AL$6:$AL$45,MATCH($A18,Campaigns!$A$6:$A$45,0))</f>
+        <v>30</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$AI$6:$AI$45,MATCH($A18,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AK$6:$AK$45,MATCH($A18,Campaigns!$A$6:$A$45,0))+INDEX(Campaigns!$AM$6:$AM$45,MATCH($A18,Campaigns!$A$6:$A$45,0))</f>
+        <v>27.09</v>
+      </c>
+      <c r="I18" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($A18,Campaigns!$A$6:$A$45,0))</f>
+        <v>3</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <f aca="false">INDEX(Campaigns!$Q$6:$Q$45,MATCH($A18,Campaigns!$A$6:$A$45,0))</f>
+        <v>88.97</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <f aca="false">INDEX(Campaigns!$Y$6:$Y$45,MATCH($A18,Campaigns!$A$6:$A$45,0))</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <f aca="false">IF(I18=0,AVERAGE(Rules!$B$15,Rules!$B$16),J18/I18)</f>
+        <v>29.6566666666667</v>
+      </c>
+      <c r="M18" s="10" t="n">
+        <f aca="false">IF(F18=0,0,G18/F18)</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="10" t="n">
+        <f aca="false">(G18+Rules!$B$37*Rules!$B$20)/(F18+Rules!$B$20)</f>
+        <v>0.00801282051282051</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <f aca="false">IF(F18=0,0,H18/F18)</f>
+        <v>0.903</v>
+      </c>
+      <c r="P18" s="10" t="n">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($A18,Campaigns!$A$6:$A$45,0))</f>
+        <v>0.669101944475666</v>
+      </c>
+      <c r="Q18" s="19" t="str">
+        <f aca="false">IF(C18="Brand defence","Brand defence: keep on",IF(G18=0,"No on-Amazon orders: pause",IF(K18&gt;0,IF(D18="ENABLED","Converting now: keep, optimize","Converting now: re-enable, optimize"),IF(D18="ENABLED","Converted before: keep, optimize","Converted before: re-enable, optimize"))))</f>
+        <v>No on-Amazon orders: pause</v>
+      </c>
+      <c r="R18" s="7" t="n">
+        <f aca="false">Rules!$B$19*L18*N18</f>
+        <v>0.0903007478632479</v>
+      </c>
+      <c r="S18" s="7" t="n">
+        <f aca="false">MAX(Rules!$B$24,R18*Rules!$B$39)</f>
+        <v>0.1</v>
+      </c>
+      <c r="T18" s="7" t="n">
+        <f aca="false">R18*Rules!$B$38</f>
+        <v>0.180601495726496</v>
+      </c>
+      <c r="U18" s="20" t="n">
+        <f aca="false">MAX(0,MIN(Rules!$B$9,T18/S18-1))</f>
+        <v>0.806014957264957</v>
+      </c>
+      <c r="V18" s="7" t="n">
+        <f aca="false">IF(O18=0,Rules!$B$7,O18)</f>
+        <v>0.903</v>
+      </c>
+      <c r="W18" s="10" t="n">
+        <f aca="false">IF(V18=0,0,S18/V18-1)</f>
+        <v>-0.889258028792913</v>
+      </c>
+      <c r="X18" s="7" t="n">
+        <f aca="false">IF(W18&lt;0,MAX(S18,V18*(1-Rules!$B$21)),MIN(S18,V18*(1+Rules!$B$22)))</f>
+        <v>0.67725</v>
+      </c>
+      <c r="Y18" s="10" t="n">
+        <f aca="false">IF(V18=0,0,X18/V18-1)</f>
+        <v>-0.25</v>
+      </c>
+      <c r="Z18" s="31" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AA18" s="20" t="n">
+        <f aca="false">IF(Z18="",U18,Z18+MAX(MIN(U18-Z18,Rules!$B$23),-Rules!$B$23))</f>
+        <v>3.36</v>
+      </c>
+      <c r="AB18" s="7" t="n">
+        <f aca="false">X18*(1+AA18)</f>
+        <v>2.95281</v>
+      </c>
+      <c r="AC18" s="32" t="n">
+        <f aca="false">F18/Rules!$B$26*7</f>
+        <v>3.62068965517241</v>
+      </c>
+      <c r="AD18" s="7" t="n">
+        <f aca="false">IF(LEFT(Q18,2)="No",0,AC18*O18*(1+Y18))</f>
+        <v>0</v>
+      </c>
+      <c r="AE18" s="21" t="n">
+        <f aca="false">IF(LEFT(Q18,2)="No",0,AC18*N18)</f>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="10" t="str">
+        <f aca="false">IF(OR(AE18=0,L18=0),"",AD18/(AE18*L18))</f>
+        <v/>
+      </c>
+      <c r="AG18" s="8" t="str">
+        <f aca="false">IF(OR(LEFT(Q18,2)="No",D18="PAUSED",ABS(Y18)&gt;Rules!$B$25,AA18&lt;&gt;Z18),"Joseph","Shayan")</f>
+        <v>Joseph</v>
+      </c>
+      <c r="AH18" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI18" s="22"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="26" t="n">
+        <f aca="false">SUM(F6:F18)</f>
+        <v>865</v>
+      </c>
+      <c r="G19" s="26" t="n">
+        <f aca="false">SUM(G6:G18)</f>
+        <v>18</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <f aca="false">SUM(H6:H18)</f>
+        <v>798.12</v>
+      </c>
+      <c r="I19" s="26" t="n">
+        <f aca="false">SUM(I6:I18)</f>
+        <v>34</v>
+      </c>
+      <c r="J19" s="24" t="n">
+        <f aca="false">SUM(J6:J18)</f>
+        <v>1072.65</v>
+      </c>
+      <c r="K19" s="26" t="n">
+        <f aca="false">SUM(K6:K18)</f>
+        <v>4</v>
+      </c>
+      <c r="L19" s="24"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="27"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="24"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="24"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="24"/>
+      <c r="W19" s="27"/>
+      <c r="X19" s="24"/>
+      <c r="Y19" s="27"/>
+      <c r="Z19" s="25"/>
+      <c r="AA19" s="25"/>
+      <c r="AB19" s="24"/>
+      <c r="AC19" s="34" t="n">
+        <f aca="false">SUMIFS(AC6:AC18,$Q$6:$Q$18,"&lt;&gt;No on-Amazon orders: pause")</f>
+        <v>96.4310344827586</v>
+      </c>
+      <c r="AD19" s="24" t="n">
+        <f aca="false">SUMIFS(AD6:AD18,$Q$6:$Q$18,"&lt;&gt;No on-Amazon orders: pause")</f>
+        <v>65.8413362068966</v>
+      </c>
+      <c r="AE19" s="28" t="n">
+        <f aca="false">SUMIFS(AE6:AE18,$Q$6:$Q$18,"&lt;&gt;No on-Amazon orders: pause")</f>
+        <v>1.76488098527251</v>
+      </c>
+      <c r="AF19" s="27" t="n">
+        <f aca="false">IF(AE19=0,"",AD19/(AE19*AVERAGE(L6:L18)))</f>
+        <v>1.16977467009758</v>
+      </c>
+      <c r="AG19" s="23"/>
+      <c r="AH19" s="23"/>
+      <c r="AI19" s="23"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="B22" s="7" t="n">
+        <f aca="false">AD19</f>
+        <v>65.8413362068966</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="B23" s="7" t="n">
+        <f aca="false">Rules!$B$6</f>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="B24" s="7" t="n">
+        <f aca="false">B23-B22</f>
+        <v>109.158663793103</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="B25" s="6" t="str">
+        <f aca="false">IF(B24&gt;=0,"Inside the $175 a week cap","Over the cap: trim the lowest-CVR campaigns first")</f>
+        <v>Inside the $175 a week cap</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="B26" s="32" t="n">
+        <f aca="false">AE19</f>
+        <v>1.76488098527251</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="B27" s="7" t="n">
+        <f aca="false">Overview!C12/15*7</f>
+        <v>110.385333333333</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="B28" s="32" t="n">
+        <f aca="false">Overview!C14/15*7</f>
+        <v>0.933333333333333</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="4"/>
+      <c r="S31" s="4"/>
+      <c r="T31" s="4"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="4"/>
+      <c r="R32" s="4"/>
+      <c r="S32" s="4"/>
+      <c r="T32" s="4"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4"/>
+      <c r="T33" s="4"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4"/>
+      <c r="S34" s="4"/>
+      <c r="T34" s="4"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="4"/>
+      <c r="S35" s="4"/>
+      <c r="T35" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A2:AI2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:Q4"/>
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="V4:AB4"/>
+    <mergeCell ref="AC4:AF4"/>
+    <mergeCell ref="AG4:AI4"/>
+    <mergeCell ref="A30:T30"/>
+    <mergeCell ref="A31:T31"/>
+    <mergeCell ref="A32:T32"/>
+    <mergeCell ref="A33:T33"/>
+    <mergeCell ref="A34:T34"/>
+    <mergeCell ref="A35:T35"/>
+  </mergeCells>
+  <conditionalFormatting sqref="Q6:Q18">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>LEFT($Q6,2)="No"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>LEFT($Q6,2)&lt;&gt;"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG6:AG18">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>$AG6="Joseph"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>LEFT($B25,6)="Inside"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>LEFT($B25,4)="Over"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <tabColor rgb="FFA6A6A6"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -9678,64 +12563,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>299</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>300</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>301</v>
+        <v>368</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>302</v>
+        <v>369</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>303</v>
+        <v>370</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>304</v>
+        <v>371</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>305</v>
+        <v>372</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>306</v>
+        <v>373</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>307</v>
+        <v>374</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>308</v>
+        <v>375</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>309</v>
+        <v>376</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>310</v>
+        <v>377</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>311</v>
+        <v>378</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>312</v>
+        <v>379</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>313</v>
+        <v>380</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>314</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B5" s="9" t="n">
         <f aca="false">COUNTIF(Campaigns!$E$6:$E$45,$A5)</f>
@@ -9796,7 +12681,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">COUNTIF(Campaigns!$E$6:$E$45,$A6)</f>
@@ -9857,7 +12742,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B7" s="9" t="n">
         <f aca="false">COUNTIF(Campaigns!$E$6:$E$45,$A7)</f>
@@ -9918,7 +12803,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">COUNTIF(Campaigns!$E$6:$E$45,$A8)</f>
@@ -9979,7 +12864,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">COUNTIF(Campaigns!$E$6:$E$45,$A9)</f>
@@ -10040,7 +12925,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">COUNTIF(Campaigns!$E$6:$E$45,$A10)</f>
@@ -10101,7 +12986,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">COUNTIF(Campaigns!$E$6:$E$45,$A11)</f>
@@ -10162,7 +13047,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">COUNTIF(Campaigns!$E$6:$E$45,$A12)</f>
@@ -10223,7 +13108,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>315</v>
+        <v>382</v>
       </c>
       <c r="B13" s="26" t="n">
         <f aca="false">SUM(B5:B12)</f>
@@ -10284,35 +13169,35 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>316</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>317</v>
+        <v>384</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>301</v>
+        <v>368</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>302</v>
+        <v>369</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>303</v>
+        <v>370</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>311</v>
+        <v>378</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>313</v>
+        <v>380</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>314</v>
+        <v>381</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">COUNTIF(Campaigns!$G$6:$G$45,$A17)</f>
@@ -10341,7 +13226,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">COUNTIF(Campaigns!$G$6:$G$45,$A18)</f>
@@ -10370,7 +13255,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">COUNTIF(Campaigns!$G$6:$G$45,$A19)</f>
@@ -10399,7 +13284,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">COUNTIF(Campaigns!$G$6:$G$45,$A20)</f>
@@ -10428,7 +13313,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B21" s="9" t="n">
         <f aca="false">COUNTIF(Campaigns!$G$6:$G$45,$A21)</f>
@@ -10457,7 +13342,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B22" s="9" t="n">
         <f aca="false">COUNTIF(Campaigns!$G$6:$G$45,$A22)</f>
@@ -10486,7 +13371,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B23" s="9" t="n">
         <f aca="false">COUNTIF(Campaigns!$G$6:$G$45,$A23)</f>
@@ -10515,7 +13400,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B24" s="9" t="n">
         <f aca="false">COUNTIF(Campaigns!$G$6:$G$45,$A24)</f>
@@ -10558,7 +13443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFA6A6A6"/>
@@ -10577,12 +13462,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>318</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="29" t="s">
-        <v>319</v>
+        <v>386</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -10594,33 +13479,33 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>320</v>
+        <v>387</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>321</v>
+        <v>388</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>322</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>323</v>
+        <v>390</v>
       </c>
       <c r="B5" s="9" t="n">
         <f aca="false">SUM(Campaigns!$AH$6:$AH$45)</f>
@@ -10646,12 +13531,12 @@
         <v>0.400811878424543</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>324</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>325</v>
+        <v>392</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">SUM(Campaigns!$AJ$6:$AJ$45)</f>
@@ -10677,12 +13562,12 @@
         <v>0.371000527903012</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>326</v>
+        <v>393</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>327</v>
+        <v>394</v>
       </c>
       <c r="B7" s="9" t="n">
         <f aca="false">SUM(Campaigns!$AL$6:$AL$45)</f>
@@ -10708,12 +13593,12 @@
         <v>0.02410150300662</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>328</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>329</v>
+        <v>396</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">SUM(Campaigns!$AN$6:$AN$45)</f>
@@ -10740,12 +13625,12 @@
         <v>0.204086090665825</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>330</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>315</v>
+        <v>382</v>
       </c>
       <c r="B9" s="26" t="n">
         <f aca="false">SUM(B5:B8)</f>
@@ -10771,16 +13656,16 @@
         <f aca="false">SUM(G5:G8)</f>
         <v>1</v>
       </c>
-      <c r="H9" s="31"/>
+      <c r="H9" s="35"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>331</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>332</v>
+        <v>399</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -10806,7 +13691,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFA6A6A6"/>
@@ -10827,73 +13712,73 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>333</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>334</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>335</v>
+        <v>402</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>336</v>
+        <v>403</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>338</v>
+        <v>404</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>339</v>
+        <v>405</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>340</v>
+        <v>406</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>341</v>
+        <v>407</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>343</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>152</v>
+        <v>409</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>160</v>
       </c>
       <c r="D5" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C5,Campaigns!$A$6:$A$45,0))</f>
         <v>PAUSED</v>
       </c>
-      <c r="E5" s="33" t="n">
+      <c r="E5" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C5,Campaigns!$A$6:$A$45,0))</f>
         <v>71</v>
       </c>
-      <c r="F5" s="33" t="n">
+      <c r="F5" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C5,Campaigns!$A$6:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="G5" s="34" t="n">
+      <c r="G5" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C5,Campaigns!$A$6:$A$45,0))</f>
         <v>63.38</v>
       </c>
-      <c r="H5" s="35" t="n">
+      <c r="H5" s="39" t="n">
         <f aca="false">IF(E5=0,0,F5/E5)</f>
         <v>0</v>
       </c>
@@ -10902,36 +13787,36 @@
         <v>Done</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>345</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>346</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>165</v>
+        <v>411</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>172</v>
       </c>
       <c r="D6" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C6,Campaigns!$A$6:$A$45,0))</f>
         <v>PAUSED</v>
       </c>
-      <c r="E6" s="33" t="n">
+      <c r="E6" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C6,Campaigns!$A$6:$A$45,0))</f>
         <v>72</v>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F6" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C6,Campaigns!$A$6:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="G6" s="34" t="n">
+      <c r="G6" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C6,Campaigns!$A$6:$A$45,0))</f>
         <v>62.18</v>
       </c>
-      <c r="H6" s="35" t="n">
+      <c r="H6" s="39" t="n">
         <f aca="false">IF(E6=0,0,F6/E6)</f>
         <v>0</v>
       </c>
@@ -10943,31 +13828,31 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>347</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>207</v>
+        <v>412</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>217</v>
       </c>
       <c r="D7" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C7,Campaigns!$A$6:$A$45,0))</f>
         <v>PAUSED</v>
       </c>
-      <c r="E7" s="33" t="n">
+      <c r="E7" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C7,Campaigns!$A$6:$A$45,0))</f>
         <v>32</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F7" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C7,Campaigns!$A$6:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="G7" s="34" t="n">
+      <c r="G7" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C7,Campaigns!$A$6:$A$45,0))</f>
         <v>27.55</v>
       </c>
-      <c r="H7" s="35" t="n">
+      <c r="H7" s="39" t="n">
         <f aca="false">IF(E7=0,0,F7/E7)</f>
         <v>0</v>
       </c>
@@ -10979,31 +13864,31 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>223</v>
+        <v>413</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>234</v>
       </c>
       <c r="D8" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C8,Campaigns!$A$6:$A$45,0))</f>
         <v>PAUSED</v>
       </c>
-      <c r="E8" s="33" t="n">
+      <c r="E8" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C8,Campaigns!$A$6:$A$45,0))</f>
         <v>18</v>
       </c>
-      <c r="F8" s="33" t="n">
+      <c r="F8" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C8,Campaigns!$A$6:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="G8" s="34" t="n">
+      <c r="G8" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C8,Campaigns!$A$6:$A$45,0))</f>
         <v>20.86</v>
       </c>
-      <c r="H8" s="35" t="n">
+      <c r="H8" s="39" t="n">
         <f aca="false">IF(E8=0,0,F8/E8)</f>
         <v>0</v>
       </c>
@@ -11015,31 +13900,31 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>349</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>176</v>
+        <v>414</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>186</v>
       </c>
       <c r="D9" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C9,Campaigns!$A$6:$A$45,0))</f>
         <v>PAUSED</v>
       </c>
-      <c r="E9" s="33" t="n">
+      <c r="E9" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C9,Campaigns!$A$6:$A$45,0))</f>
         <v>50</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C9,Campaigns!$A$6:$A$45,0))</f>
         <v>2</v>
       </c>
-      <c r="G9" s="34" t="n">
+      <c r="G9" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C9,Campaigns!$A$6:$A$45,0))</f>
         <v>44.85</v>
       </c>
-      <c r="H9" s="35" t="n">
+      <c r="H9" s="39" t="n">
         <f aca="false">IF(E9=0,0,F9/E9)</f>
         <v>0.04</v>
       </c>
@@ -11048,36 +13933,36 @@
         <v>Done</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>350</v>
+        <v>415</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>351</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>211</v>
+        <v>416</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>221</v>
       </c>
       <c r="D10" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C10,Campaigns!$A$6:$A$45,0))</f>
         <v>PAUSED</v>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="E10" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C10,Campaigns!$A$6:$A$45,0))</f>
         <v>28</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F10" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C10,Campaigns!$A$6:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="G10" s="34" t="n">
+      <c r="G10" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C10,Campaigns!$A$6:$A$45,0))</f>
         <v>27.35</v>
       </c>
-      <c r="H10" s="35" t="n">
+      <c r="H10" s="39" t="n">
         <f aca="false">IF(E10=0,0,F10/E10)</f>
         <v>0</v>
       </c>
@@ -11086,36 +13971,36 @@
         <v>Done</v>
       </c>
       <c r="J10" s="19" t="s">
-        <v>352</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>232</v>
+        <v>418</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>243</v>
       </c>
       <c r="D11" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C11,Campaigns!$A$6:$A$45,0))</f>
         <v>PAUSED</v>
       </c>
-      <c r="E11" s="33" t="n">
+      <c r="E11" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C11,Campaigns!$A$6:$A$45,0))</f>
         <v>43</v>
       </c>
-      <c r="F11" s="33" t="n">
+      <c r="F11" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C11,Campaigns!$A$6:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="34" t="n">
+      <c r="G11" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C11,Campaigns!$A$6:$A$45,0))</f>
         <v>19.66</v>
       </c>
-      <c r="H11" s="35" t="n">
+      <c r="H11" s="39" t="n">
         <f aca="false">IF(E11=0,0,F11/E11)</f>
         <v>0</v>
       </c>
@@ -11127,31 +14012,31 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>198</v>
+        <v>418</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>207</v>
       </c>
       <c r="D12" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C12,Campaigns!$A$6:$A$45,0))</f>
         <v>ENABLED</v>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="E12" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C12,Campaigns!$A$6:$A$45,0))</f>
         <v>18</v>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F12" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C12,Campaigns!$A$6:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="G12" s="34" t="n">
+      <c r="G12" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C12,Campaigns!$A$6:$A$45,0))</f>
         <v>28.44</v>
       </c>
-      <c r="H12" s="35" t="n">
+      <c r="H12" s="39" t="n">
         <f aca="false">IF(E12=0,0,F12/E12)</f>
         <v>0</v>
       </c>
@@ -11160,36 +14045,36 @@
         <v>Still running: pause</v>
       </c>
       <c r="J12" s="19" t="s">
-        <v>354</v>
+        <v>419</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>274</v>
+        <v>418</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>284</v>
       </c>
       <c r="D13" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C13,Campaigns!$A$6:$A$45,0))</f>
         <v>ENABLED</v>
       </c>
-      <c r="E13" s="33" t="n">
+      <c r="E13" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C13,Campaigns!$A$6:$A$45,0))</f>
         <v>2</v>
       </c>
-      <c r="F13" s="33" t="n">
+      <c r="F13" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C13,Campaigns!$A$6:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="G13" s="34" t="n">
+      <c r="G13" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C13,Campaigns!$A$6:$A$45,0))</f>
         <v>6.03</v>
       </c>
-      <c r="H13" s="35" t="n">
+      <c r="H13" s="39" t="n">
         <f aca="false">IF(E13=0,0,F13/E13)</f>
         <v>0</v>
       </c>
@@ -11198,36 +14083,36 @@
         <v>Still running: pause</v>
       </c>
       <c r="J13" s="19" t="s">
-        <v>354</v>
+        <v>419</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>355</v>
+        <v>420</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>227</v>
+        <v>418</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>238</v>
       </c>
       <c r="D14" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C14,Campaigns!$A$6:$A$45,0))</f>
         <v>ENABLED</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E14" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C14,Campaigns!$A$6:$A$45,0))</f>
         <v>11</v>
       </c>
-      <c r="F14" s="33" t="n">
+      <c r="F14" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C14,Campaigns!$A$6:$A$45,0))</f>
         <v>0</v>
       </c>
-      <c r="G14" s="34" t="n">
+      <c r="G14" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C14,Campaigns!$A$6:$A$45,0))</f>
         <v>20.64</v>
       </c>
-      <c r="H14" s="35" t="n">
+      <c r="H14" s="39" t="n">
         <f aca="false">IF(E14=0,0,F14/E14)</f>
         <v>0</v>
       </c>
@@ -11236,19 +14121,19 @@
         <v>Still running: pause</v>
       </c>
       <c r="J14" s="19" t="s">
-        <v>356</v>
+        <v>421</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="36" t="str">
+      <c r="B16" s="40" t="str">
         <f aca="false">COUNTIF(I5:I13,"Done")&amp;" of "&amp;COUNTA(A5:A13)</f>
         <v>7 of 9</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>357</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -11270,7 +14155,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFA6A6A6"/>
@@ -11290,221 +14175,221 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>358</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>359</v>
+        <v>424</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>360</v>
+        <v>425</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>361</v>
+        <v>426</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>362</v>
+        <v>427</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>363</v>
+        <v>428</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>364</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>365</v>
+        <v>430</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>366</v>
+        <v>431</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="D4" s="34" t="n">
+        <v>432</v>
+      </c>
+      <c r="D4" s="38" t="n">
         <f aca="false">Campaigns!I46</f>
         <v>210.88</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>368</v>
+        <v>433</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>369</v>
+        <v>434</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>370</v>
+        <v>435</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>371</v>
+        <v>436</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="D5" s="34" t="n">
+        <v>438</v>
+      </c>
+      <c r="D5" s="38" t="n">
         <f aca="false">Overview!$C$12/15</f>
         <v>15.7693333333333</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>374</v>
+        <v>439</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>375</v>
+        <v>440</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>376</v>
+        <v>441</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>377</v>
+        <v>442</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>378</v>
+        <v>443</v>
       </c>
       <c r="D6" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH("94080520861158",Campaigns!$A$6:$A$45,0))</f>
         <v>ENABLED</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>379</v>
+        <v>444</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>380</v>
+        <v>445</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>381</v>
+        <v>446</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>382</v>
+        <v>447</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>383</v>
+        <v>448</v>
       </c>
       <c r="D7" s="19" t="str">
         <f aca="false">COUNTIFS(Campaigns!$G$6:$G$45,"Phase 0: run*",Campaigns!$E$6:$E$45,"Boho core",Campaigns!$H$6:$H$45,"ENABLED")&amp;" of 5"</f>
         <v>1 of 5</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>384</v>
+        <v>449</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>385</v>
+        <v>450</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>386</v>
+        <v>451</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>387</v>
+        <v>452</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>388</v>
-      </c>
-      <c r="D8" s="33" t="n">
+        <v>453</v>
+      </c>
+      <c r="D8" s="37" t="n">
         <f aca="false">COUNTIF(Campaigns!$AS$6:$AS$45,"Above +300% cap")</f>
         <v>10</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>389</v>
+        <v>454</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>390</v>
+        <v>455</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>391</v>
+        <v>456</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>377</v>
+        <v>442</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>392</v>
-      </c>
-      <c r="D9" s="34" t="n">
+        <v>457</v>
+      </c>
+      <c r="D9" s="38" t="n">
         <f aca="false">IF(INDEX(Campaigns!$W$6:$W$45,MATCH("43669682187702",Campaigns!$A$6:$A$45,0))=0,0,INDEX(Campaigns!$X$6:$X$45,MATCH("43669682187702",Campaigns!$A$6:$A$45,0))/INDEX(Campaigns!$W$6:$W$45,MATCH("43669682187702",Campaigns!$A$6:$A$45,0)))</f>
         <v>1.21928571428571</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>393</v>
+        <v>458</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>394</v>
+        <v>459</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>395</v>
+        <v>460</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>396</v>
+        <v>461</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>397</v>
-      </c>
-      <c r="D10" s="37" t="n">
+        <v>462</v>
+      </c>
+      <c r="D10" s="41" t="n">
         <v>80.07</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>398</v>
+        <v>463</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>399</v>
+        <v>464</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>400</v>
+        <v>465</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>401</v>
+        <v>466</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="D11" s="33" t="n">
+        <v>467</v>
+      </c>
+      <c r="D11" s="37" t="n">
         <f aca="false">COUNTIFS(Campaigns!$G$6:$G$45,"Not in Phase 0*",Campaigns!$H$6:$H$45,"ENABLED")+COUNTIFS(Campaigns!$G$6:$G$45,"Exclude*",Campaigns!$H$6:$H$45,"ENABLED")+COUNTIFS(Campaigns!$G$6:$G$45,"Phase 0: stop list",Campaigns!$H$6:$H$45,"ENABLED")</f>
         <v>19</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>403</v>
+        <v>468</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>404</v>
+        <v>469</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -11519,13 +14404,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFFFC000"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -11541,48 +14426,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>405</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>340</v>
-      </c>
       <c r="K3" s="5" t="s">
-        <v>408</v>
+        <v>472</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>409</v>
+        <v>473</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>410</v>
+        <v>474</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11590,305 +14475,520 @@
         <v>1</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>147</v>
+        <v>157</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>155</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>377</v>
+        <v>442</v>
       </c>
       <c r="E4" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C4,Campaigns!$A$6:$A$45,0))</f>
         <v>PAUSED</v>
       </c>
-      <c r="F4" s="33" t="n">
+      <c r="F4" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C4,Campaigns!$A$6:$A$45,0))</f>
         <v>125</v>
       </c>
-      <c r="G4" s="33" t="n">
+      <c r="G4" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C4,Campaigns!$A$6:$A$45,0))</f>
         <v>3</v>
       </c>
-      <c r="H4" s="35" t="n">
+      <c r="H4" s="39" t="n">
         <f aca="false">IF(F4=0,0,G4/F4)</f>
         <v>0.024</v>
       </c>
-      <c r="I4" s="35" t="n">
+      <c r="I4" s="39" t="n">
         <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($C4,Campaigns!$A$6:$A$45,0))</f>
         <v>1.14536247993084</v>
       </c>
-      <c r="J4" s="34" t="n">
+      <c r="J4" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C4,Campaigns!$A$6:$A$45,0))</f>
         <v>92.74</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
+        <v>475</v>
+      </c>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>125</v>
+        <v>135</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>133</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>377</v>
+        <v>442</v>
       </c>
       <c r="E5" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C5,Campaigns!$A$6:$A$45,0))</f>
         <v>PAUSED</v>
       </c>
-      <c r="F5" s="33" t="n">
+      <c r="F5" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C5,Campaigns!$A$6:$A$45,0))</f>
         <v>187</v>
       </c>
-      <c r="G5" s="33" t="n">
+      <c r="G5" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C5,Campaigns!$A$6:$A$45,0))</f>
         <v>3</v>
       </c>
-      <c r="H5" s="35" t="n">
+      <c r="H5" s="39" t="n">
         <f aca="false">IF(F5=0,0,G5/F5)</f>
         <v>0.0160427807486631</v>
       </c>
-      <c r="I5" s="35" t="n">
+      <c r="I5" s="39" t="n">
         <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($C5,Campaigns!$A$6:$A$45,0))</f>
         <v>1.55737889176127</v>
       </c>
-      <c r="J5" s="34" t="n">
+      <c r="J5" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C5,Campaigns!$A$6:$A$45,0))</f>
         <v>138.56</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>412</v>
-      </c>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
+        <v>476</v>
+      </c>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>181</v>
+        <v>188</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>186</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>413</v>
+        <v>477</v>
       </c>
       <c r="E6" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C6,Campaigns!$A$6:$A$45,0))</f>
         <v>PAUSED</v>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F6" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C6,Campaigns!$A$6:$A$45,0))</f>
-        <v>44</v>
-      </c>
-      <c r="G6" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C6,Campaigns!$A$6:$A$45,0))</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="39" t="n">
         <f aca="false">IF(F6=0,0,G6/F6)</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="35" t="str">
+        <v>0.04</v>
+      </c>
+      <c r="I6" s="39" t="n">
         <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($C6,Campaigns!$A$6:$A$45,0))</f>
-        <v/>
-      </c>
-      <c r="J6" s="34" t="n">
+        <v>0.723620522749274</v>
+      </c>
+      <c r="J6" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C6,Campaigns!$A$6:$A$45,0))</f>
-        <v>42.81</v>
+        <v>44.85</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>478</v>
+      </c>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>152</v>
+        <v>197</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>195</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>415</v>
+        <v>479</v>
       </c>
       <c r="E7" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C7,Campaigns!$A$6:$A$45,0))</f>
         <v>PAUSED</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F7" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C7,Campaigns!$A$6:$A$45,0))</f>
-        <v>71</v>
-      </c>
-      <c r="G7" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="G7" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C7,Campaigns!$A$6:$A$45,0))</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="39" t="n">
         <f aca="false">IF(F7=0,0,G7/F7)</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="35" t="str">
+        <v>0.0285714285714286</v>
+      </c>
+      <c r="I7" s="39" t="n">
         <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($C7,Campaigns!$A$6:$A$45,0))</f>
-        <v/>
-      </c>
-      <c r="J7" s="34" t="n">
+        <v>1.05687339239783</v>
+      </c>
+      <c r="J7" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C7,Campaigns!$A$6:$A$45,0))</f>
-        <v>63.38</v>
+        <v>36.98</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>480</v>
+      </c>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>176</v>
+        <v>347</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>166</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>416</v>
+        <v>479</v>
       </c>
       <c r="E8" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C8,Campaigns!$A$6:$A$45,0))</f>
         <v>PAUSED</v>
       </c>
-      <c r="F8" s="33" t="n">
+      <c r="F8" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C8,Campaigns!$A$6:$A$45,0))</f>
-        <v>50</v>
-      </c>
-      <c r="G8" s="33" t="n">
+        <v>77</v>
+      </c>
+      <c r="G8" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C8,Campaigns!$A$6:$A$45,0))</f>
-        <v>2</v>
-      </c>
-      <c r="H8" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="39" t="n">
         <f aca="false">IF(F8=0,0,G8/F8)</f>
-        <v>0.04</v>
-      </c>
-      <c r="I8" s="35" t="n">
+        <v>0.012987012987013</v>
+      </c>
+      <c r="I8" s="39" t="n">
         <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($C8,Campaigns!$A$6:$A$45,0))</f>
-        <v>0.723620522749274</v>
-      </c>
-      <c r="J8" s="34" t="n">
+        <v>2.33308632826973</v>
+      </c>
+      <c r="J8" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C8,Campaigns!$A$6:$A$45,0))</f>
-        <v>44.85</v>
+        <v>62.97</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>417</v>
-      </c>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
+        <v>480</v>
+      </c>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>418</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>105</v>
+        <v>348</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>199</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>419</v>
+        <v>130</v>
       </c>
       <c r="E9" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C9,Campaigns!$A$6:$A$45,0))</f>
-        <v>ENABLED</v>
-      </c>
-      <c r="F9" s="33" t="n">
+        <v>PAUSED</v>
+      </c>
+      <c r="F9" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C9,Campaigns!$A$6:$A$45,0))</f>
-        <v>1063</v>
-      </c>
-      <c r="G9" s="33" t="n">
+        <v>38</v>
+      </c>
+      <c r="G9" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C9,Campaigns!$A$6:$A$45,0))</f>
-        <v>9</v>
-      </c>
-      <c r="H9" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="39" t="n">
         <f aca="false">IF(F9=0,0,G9/F9)</f>
-        <v>0.00846660395108184</v>
-      </c>
-      <c r="I9" s="35" t="n">
+        <v>0.0263157894736842</v>
+      </c>
+      <c r="I9" s="39" t="n">
         <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($C9,Campaigns!$A$6:$A$45,0))</f>
-        <v>0.845604609239687</v>
-      </c>
-      <c r="J9" s="34" t="n">
+        <v>0.940268648185196</v>
+      </c>
+      <c r="J9" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C9,Campaigns!$A$6:$A$45,0))</f>
-        <v>239.23</v>
+        <v>32.9</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
+        <v>480</v>
+      </c>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="n">
         <v>7</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>116</v>
+        <v>481</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>146</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>421</v>
+        <v>482</v>
       </c>
       <c r="E10" s="19" t="str">
         <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C10,Campaigns!$A$6:$A$45,0))</f>
         <v>ENABLED</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F10" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C10,Campaigns!$A$6:$A$45,0))</f>
-        <v>476</v>
-      </c>
-      <c r="G10" s="33" t="n">
+        <v>67</v>
+      </c>
+      <c r="G10" s="37" t="n">
         <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C10,Campaigns!$A$6:$A$45,0))</f>
-        <v>5</v>
-      </c>
-      <c r="H10" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="39" t="n">
         <f aca="false">IF(F10=0,0,G10/F10)</f>
-        <v>0.0105042016806723</v>
-      </c>
-      <c r="I10" s="35" t="n">
+        <v>0.0149253731343284</v>
+      </c>
+      <c r="I10" s="39" t="n">
         <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($C10,Campaigns!$A$6:$A$45,0))</f>
-        <v>1.05319642265651</v>
-      </c>
-      <c r="J10" s="34" t="n">
+        <v>2.94598456701915</v>
+      </c>
+      <c r="J10" s="38" t="n">
         <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C10,Campaigns!$A$6:$A$45,0))</f>
-        <v>158.98</v>
+        <v>103.08</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>422</v>
-      </c>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
-        <v>423</v>
+        <v>483</v>
+      </c>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>484</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>485</v>
+      </c>
+      <c r="E11" s="19" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C11,Campaigns!$A$6:$A$45,0))</f>
+        <v>ENABLED</v>
+      </c>
+      <c r="F11" s="37" t="n">
+        <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C11,Campaigns!$A$6:$A$45,0))</f>
+        <v>184</v>
+      </c>
+      <c r="G11" s="37" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C11,Campaigns!$A$6:$A$45,0))</f>
+        <v>4</v>
+      </c>
+      <c r="H11" s="39" t="n">
+        <f aca="false">IF(F11=0,0,G11/F11)</f>
+        <v>0.0217391304347826</v>
+      </c>
+      <c r="I11" s="39" t="n">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($C11,Campaigns!$A$6:$A$45,0))</f>
+        <v>0.850679032792315</v>
+      </c>
+      <c r="J11" s="38" t="n">
+        <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C11,Campaigns!$A$6:$A$45,0))</f>
+        <v>128.41</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>486</v>
+      </c>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="E12" s="19" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C12,Campaigns!$A$6:$A$45,0))</f>
+        <v>PAUSED</v>
+      </c>
+      <c r="F12" s="37" t="n">
+        <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C12,Campaigns!$A$6:$A$45,0))</f>
+        <v>44</v>
+      </c>
+      <c r="G12" s="37" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C12,Campaigns!$A$6:$A$45,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="39" t="n">
+        <f aca="false">IF(F12=0,0,G12/F12)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="39" t="str">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($C12,Campaigns!$A$6:$A$45,0))</f>
+        <v/>
+      </c>
+      <c r="J12" s="38" t="n">
+        <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C12,Campaigns!$A$6:$A$45,0))</f>
+        <v>42.81</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>489</v>
+      </c>
+      <c r="E13" s="19" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C13,Campaigns!$A$6:$A$45,0))</f>
+        <v>PAUSED</v>
+      </c>
+      <c r="F13" s="37" t="n">
+        <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C13,Campaigns!$A$6:$A$45,0))</f>
+        <v>71</v>
+      </c>
+      <c r="G13" s="37" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C13,Campaigns!$A$6:$A$45,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="39" t="n">
+        <f aca="false">IF(F13=0,0,G13/F13)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="39" t="str">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($C13,Campaigns!$A$6:$A$45,0))</f>
+        <v/>
+      </c>
+      <c r="J13" s="38" t="n">
+        <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C13,Campaigns!$A$6:$A$45,0))</f>
+        <v>63.38</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>490</v>
+      </c>
+      <c r="E14" s="19" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C14,Campaigns!$A$6:$A$45,0))</f>
+        <v>ENABLED</v>
+      </c>
+      <c r="F14" s="37" t="n">
+        <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C14,Campaigns!$A$6:$A$45,0))</f>
+        <v>1063</v>
+      </c>
+      <c r="G14" s="37" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C14,Campaigns!$A$6:$A$45,0))</f>
+        <v>9</v>
+      </c>
+      <c r="H14" s="39" t="n">
+        <f aca="false">IF(F14=0,0,G14/F14)</f>
+        <v>0.00846660395108184</v>
+      </c>
+      <c r="I14" s="39" t="n">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($C14,Campaigns!$A$6:$A$45,0))</f>
+        <v>0.845604609239687</v>
+      </c>
+      <c r="J14" s="38" t="n">
+        <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C14,Campaigns!$A$6:$A$45,0))</f>
+        <v>239.23</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>491</v>
+      </c>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15" s="19" t="str">
+        <f aca="false">INDEX(Campaigns!$H$6:$H$45,MATCH($C15,Campaigns!$A$6:$A$45,0))</f>
+        <v>ENABLED</v>
+      </c>
+      <c r="F15" s="37" t="n">
+        <f aca="false">INDEX(Campaigns!$N$6:$N$45,MATCH($C15,Campaigns!$A$6:$A$45,0))</f>
+        <v>1063</v>
+      </c>
+      <c r="G15" s="37" t="n">
+        <f aca="false">INDEX(Campaigns!$P$6:$P$45,MATCH($C15,Campaigns!$A$6:$A$45,0))</f>
+        <v>9</v>
+      </c>
+      <c r="H15" s="39" t="n">
+        <f aca="false">IF(F15=0,0,G15/F15)</f>
+        <v>0.00846660395108184</v>
+      </c>
+      <c r="I15" s="39" t="n">
+        <f aca="false">INDEX(Campaigns!$U$6:$U$45,MATCH($C15,Campaigns!$A$6:$A$45,0))</f>
+        <v>0.845604609239687</v>
+      </c>
+      <c r="J15" s="38" t="n">
+        <f aca="false">INDEX(Campaigns!$O$6:$O$45,MATCH($C15,Campaigns!$A$6:$A$45,0))</f>
+        <v>239.23</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="s">
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -11902,13 +15002,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFA6A6A6"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -11918,290 +15018,426 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>424</v>
+        <v>495</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>425</v>
+        <v>496</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>426</v>
+        <v>497</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>427</v>
+        <v>498</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>428</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="39" t="s">
-        <v>429</v>
-      </c>
-      <c r="B5" s="40" t="n">
+      <c r="A5" s="43" t="s">
+        <v>500</v>
+      </c>
+      <c r="B5" s="44" t="n">
         <v>25</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>430</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="39" t="s">
-        <v>431</v>
-      </c>
-      <c r="B6" s="40" t="n">
+      <c r="A6" s="43" t="s">
+        <v>502</v>
+      </c>
+      <c r="B6" s="44" t="n">
         <v>175</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>432</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="39" t="s">
-        <v>433</v>
-      </c>
-      <c r="B7" s="41" t="n">
+      <c r="A7" s="43" t="s">
+        <v>504</v>
+      </c>
+      <c r="B7" s="45" t="n">
         <v>0.45</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>434</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="39" t="s">
-        <v>435</v>
-      </c>
-      <c r="B8" s="41" t="n">
+      <c r="A8" s="43" t="s">
+        <v>506</v>
+      </c>
+      <c r="B8" s="45" t="n">
         <v>0.5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>436</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="39" t="s">
-        <v>437</v>
-      </c>
-      <c r="B9" s="42" t="n">
+      <c r="A9" s="43" t="s">
+        <v>508</v>
+      </c>
+      <c r="B9" s="46" t="n">
         <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>438</v>
+        <v>509</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="39" t="s">
-        <v>439</v>
-      </c>
-      <c r="B10" s="43" t="n">
+      <c r="A10" s="43" t="s">
+        <v>510</v>
+      </c>
+      <c r="B10" s="47" t="n">
         <v>20</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>440</v>
+        <v>511</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="39" t="s">
-        <v>441</v>
-      </c>
-      <c r="B11" s="43" t="n">
+      <c r="A11" s="43" t="s">
+        <v>512</v>
+      </c>
+      <c r="B11" s="47" t="n">
         <v>100</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>442</v>
+        <v>513</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="39" t="s">
-        <v>443</v>
-      </c>
-      <c r="B12" s="44" t="n">
+      <c r="A12" s="43" t="s">
+        <v>514</v>
+      </c>
+      <c r="B12" s="48" t="n">
         <v>0.04</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>444</v>
+        <v>515</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="39" t="s">
-        <v>445</v>
-      </c>
-      <c r="B13" s="44" t="n">
+      <c r="A13" s="43" t="s">
+        <v>516</v>
+      </c>
+      <c r="B13" s="48" t="n">
         <v>0.02</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>446</v>
+        <v>517</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="39" t="s">
-        <v>447</v>
-      </c>
-      <c r="B14" s="45" t="n">
+      <c r="A14" s="43" t="s">
+        <v>518</v>
+      </c>
+      <c r="B14" s="49" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>448</v>
+        <v>519</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="39" t="s">
-        <v>449</v>
-      </c>
-      <c r="B15" s="41" t="n">
+      <c r="A15" s="43" t="s">
+        <v>520</v>
+      </c>
+      <c r="B15" s="45" t="n">
         <v>26.99</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>450</v>
+        <v>521</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="39" t="s">
-        <v>451</v>
-      </c>
-      <c r="B16" s="41" t="n">
+      <c r="A16" s="43" t="s">
+        <v>522</v>
+      </c>
+      <c r="B16" s="45" t="n">
         <v>34.99</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>450</v>
+        <v>521</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="39" t="s">
-        <v>452</v>
-      </c>
-      <c r="B17" s="41" t="n">
+      <c r="A17" s="43" t="s">
+        <v>523</v>
+      </c>
+      <c r="B17" s="45" t="n">
         <v>3.44</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>453</v>
+        <v>524</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="39" t="s">
-        <v>454</v>
-      </c>
-      <c r="B18" s="41" t="n">
+      <c r="A18" s="43" t="s">
+        <v>525</v>
+      </c>
+      <c r="B18" s="45" t="n">
         <v>4.37</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>455</v>
+        <v>526</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="43" t="s">
+        <v>527</v>
+      </c>
+      <c r="B19" s="48" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="36" t="s">
-        <v>456</v>
+      <c r="A20" s="43" t="s">
+        <v>529</v>
+      </c>
+      <c r="B20" s="47" t="n">
+        <v>50</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="39" t="s">
-        <v>457</v>
-      </c>
-      <c r="B21" s="46" t="n">
+      <c r="A21" s="43" t="s">
+        <v>531</v>
+      </c>
+      <c r="B21" s="48" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="43" t="s">
+        <v>533</v>
+      </c>
+      <c r="B22" s="48" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="43" t="s">
+        <v>535</v>
+      </c>
+      <c r="B23" s="46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="43" t="s">
+        <v>537</v>
+      </c>
+      <c r="B24" s="45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="43" t="s">
+        <v>539</v>
+      </c>
+      <c r="B25" s="48" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="43" t="s">
+        <v>541</v>
+      </c>
+      <c r="B26" s="47" t="n">
+        <v>58</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="40" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="43" t="s">
+        <v>544</v>
+      </c>
+      <c r="B29" s="50" t="n">
         <f aca="false">Rules!$B$17/Rules!$B$15</f>
         <v>0.127454612819563</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="39" t="s">
-        <v>459</v>
-      </c>
-      <c r="B22" s="46" t="n">
+      <c r="C29" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="43" t="s">
+        <v>546</v>
+      </c>
+      <c r="B30" s="50" t="n">
         <f aca="false">Rules!$B$18/Rules!$B$16</f>
         <v>0.124892826521863</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="39" t="s">
-        <v>460</v>
-      </c>
-      <c r="B23" s="46" t="n">
-        <f aca="false">AVERAGE(B21:B22)</f>
+      <c r="C30" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="43" t="s">
+        <v>547</v>
+      </c>
+      <c r="B31" s="50" t="n">
+        <f aca="false">AVERAGE(B29:B30)</f>
         <v>0.126173719670713</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="39" t="s">
-        <v>462</v>
-      </c>
-      <c r="B24" s="46" t="n">
-        <f aca="false">B23*Rules!$B$14</f>
+      <c r="C31" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="43" t="s">
+        <v>549</v>
+      </c>
+      <c r="B32" s="50" t="n">
+        <f aca="false">B31*Rules!$B$14</f>
         <v>0.378521159012139</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="39" t="s">
-        <v>464</v>
-      </c>
-      <c r="B25" s="47" t="n">
+      <c r="C32" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="43" t="s">
+        <v>551</v>
+      </c>
+      <c r="B33" s="51" t="n">
         <f aca="false">Rules!$B$17*0.01</f>
         <v>0.0344</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="39" t="s">
-        <v>466</v>
-      </c>
-      <c r="B26" s="47" t="n">
+      <c r="C33" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="43" t="s">
+        <v>553</v>
+      </c>
+      <c r="B34" s="51" t="n">
         <f aca="false">Rules!$B$18*0.01</f>
         <v>0.0437</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="39" t="s">
-        <v>468</v>
-      </c>
-      <c r="B27" s="46" t="n">
+      <c r="C34" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="43" t="s">
+        <v>555</v>
+      </c>
+      <c r="B35" s="50" t="n">
         <f aca="false">Overview!$C$15/Rules!$B$17</f>
         <v>0.319821525148729</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="39" t="s">
-        <v>470</v>
-      </c>
-      <c r="B28" s="46" t="n">
+      <c r="C35" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="43" t="s">
+        <v>557</v>
+      </c>
+      <c r="B36" s="50" t="n">
         <f aca="false">Overview!$C$15/Rules!$B$18</f>
         <v>0.251758820712043</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="29" t="s">
-        <v>471</v>
-      </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
+      <c r="C36" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="43" t="s">
+        <v>558</v>
+      </c>
+      <c r="B37" s="50" t="n">
+        <f aca="false">IF(SUM(Placements!B5:B7)=0,0,SUM(Placements!D5:D7)/SUM(Placements!B5:B7))</f>
+        <v>0.0128205128205128</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="43" t="s">
+        <v>560</v>
+      </c>
+      <c r="B38" s="52" t="n">
+        <f aca="false">IF(B37=0,0,Placements!E5/B37)</f>
+        <v>2</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="43" t="s">
+        <v>562</v>
+      </c>
+      <c r="B39" s="52" t="n">
+        <f aca="false">IF(B37=0,0,Placements!E6/B37)</f>
+        <v>0.507592190889371</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="43" t="s">
+        <v>564</v>
+      </c>
+      <c r="B40" s="53" t="n">
+        <f aca="false">IF(B39=0,0,MIN(Rules!$B$9,B38/B39-1))</f>
+        <v>2.94017094017094</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="29" t="s">
+        <v>566</v>
+      </c>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A42:C42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
